--- a/research/traditional_assets/database/data/qatar/qatar_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_oilfield_svcs_equip.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08567835674138913</v>
+        <v>0.08563317838464773</v>
       </c>
       <c r="C2">
-        <v>156.8460301072068</v>
+        <v>155.3685611755052</v>
       </c>
       <c r="D2">
-        <v>135.6460301072069</v>
+        <v>135.7285611755052</v>
       </c>
       <c r="E2">
-        <v>-16.6</v>
+        <v>-15.04</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="G2">
         <v>21.2</v>
@@ -1573,28 +1573,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.078468</v>
       </c>
       <c r="N2">
-        <v>10.56111111111111</v>
+        <v>10.48264311111111</v>
       </c>
       <c r="O2">
-        <v>1.056111111111111</v>
+        <v>1.048264311111111</v>
       </c>
       <c r="P2">
-        <v>9.504999999999999</v>
+        <v>9.434378799999998</v>
       </c>
       <c r="Q2">
-        <v>11.055</v>
+        <v>10.9843788</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08567835674138913</v>
+        <v>0.08604088725721994</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8065746613658668</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>134.5913125237181</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08563317838464773</v>
+        <v>0.08558800002790636</v>
       </c>
       <c r="C3">
-        <v>155.3685611755052</v>
+        <v>153.8911927336447</v>
       </c>
       <c r="D3">
-        <v>135.7285611755052</v>
+        <v>135.8111927336447</v>
       </c>
       <c r="E3">
-        <v>-15.04</v>
+        <v>-13.48</v>
       </c>
       <c r="F3">
-        <v>1.56</v>
+        <v>3.12</v>
       </c>
       <c r="G3">
         <v>21.2</v>
@@ -1655,28 +1655,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M3">
-        <v>0.078468</v>
+        <v>0.156936</v>
       </c>
       <c r="N3">
-        <v>10.48264311111111</v>
+        <v>10.40417511111111</v>
       </c>
       <c r="O3">
-        <v>1.048264311111111</v>
+        <v>1.040417511111111</v>
       </c>
       <c r="P3">
-        <v>9.434378799999998</v>
+        <v>9.3637576</v>
       </c>
       <c r="Q3">
-        <v>10.9843788</v>
+        <v>10.9137576</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08604088725721994</v>
+        <v>0.08641081635500648</v>
       </c>
       <c r="T3">
-        <v>0.8065746613658668</v>
+        <v>0.8139893944175847</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.5913125237181</v>
+        <v>67.29565626185904</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08558800002790636</v>
+        <v>0.08554282167116498</v>
       </c>
       <c r="C4">
-        <v>153.8911927336447</v>
+        <v>152.4139249652715</v>
       </c>
       <c r="D4">
-        <v>135.8111927336447</v>
+        <v>135.8939249652716</v>
       </c>
       <c r="E4">
-        <v>-13.48</v>
+        <v>-11.92</v>
       </c>
       <c r="F4">
-        <v>3.12</v>
+        <v>4.68</v>
       </c>
       <c r="G4">
         <v>21.2</v>
@@ -1737,28 +1737,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M4">
-        <v>0.156936</v>
+        <v>0.235404</v>
       </c>
       <c r="N4">
-        <v>10.40417511111111</v>
+        <v>10.32570711111111</v>
       </c>
       <c r="O4">
-        <v>1.040417511111111</v>
+        <v>1.032570711111111</v>
       </c>
       <c r="P4">
-        <v>9.3637576</v>
+        <v>9.293136399999998</v>
       </c>
       <c r="Q4">
-        <v>10.9137576</v>
+        <v>10.8431364</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08641081635500648</v>
+        <v>0.0867883728568711</v>
       </c>
       <c r="T4">
-        <v>0.8139893944175847</v>
+        <v>0.8215570085631523</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.29565626185904</v>
+        <v>44.86377084123936</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08554282167116498</v>
+        <v>0.08549764331442357</v>
       </c>
       <c r="C5">
-        <v>152.4139249652715</v>
+        <v>150.9367580544802</v>
       </c>
       <c r="D5">
-        <v>135.8939249652716</v>
+        <v>135.9767580544803</v>
       </c>
       <c r="E5">
-        <v>-11.92</v>
+        <v>-10.36</v>
       </c>
       <c r="F5">
-        <v>4.68</v>
+        <v>6.24</v>
       </c>
       <c r="G5">
         <v>21.2</v>
@@ -1819,28 +1819,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M5">
-        <v>0.235404</v>
+        <v>0.313872</v>
       </c>
       <c r="N5">
-        <v>10.32570711111111</v>
+        <v>10.24723911111111</v>
       </c>
       <c r="O5">
-        <v>1.032570711111111</v>
+        <v>1.024723911111111</v>
       </c>
       <c r="P5">
-        <v>9.293136399999998</v>
+        <v>9.222515199999998</v>
       </c>
       <c r="Q5">
-        <v>10.8431364</v>
+        <v>10.7725152</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0867883728568711</v>
+        <v>0.08717379511919122</v>
       </c>
       <c r="T5">
-        <v>0.8215570085631523</v>
+        <v>0.8292822813367527</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.86377084123936</v>
+        <v>33.64782813092952</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08549764331442357</v>
+        <v>0.08545246495768218</v>
       </c>
       <c r="C6">
-        <v>150.9367580544802</v>
+        <v>149.459692185814</v>
       </c>
       <c r="D6">
-        <v>135.9767580544803</v>
+        <v>136.059692185814</v>
       </c>
       <c r="E6">
-        <v>-10.36</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="F6">
-        <v>6.24</v>
+        <v>7.800000000000001</v>
       </c>
       <c r="G6">
         <v>21.2</v>
@@ -1901,28 +1901,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M6">
-        <v>0.313872</v>
+        <v>0.39234</v>
       </c>
       <c r="N6">
-        <v>10.24723911111111</v>
+        <v>10.16877111111111</v>
       </c>
       <c r="O6">
-        <v>1.024723911111111</v>
+        <v>1.016877111111111</v>
       </c>
       <c r="P6">
-        <v>9.222515199999998</v>
+        <v>9.151893999999999</v>
       </c>
       <c r="Q6">
-        <v>10.7725152</v>
+        <v>10.701894</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08717379511919122</v>
+        <v>0.0875673315344023</v>
       </c>
       <c r="T6">
-        <v>0.8292822813367527</v>
+        <v>0.8371701914319025</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.64782813092952</v>
+        <v>26.91826250474361</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08545246495768218</v>
+        <v>0.08540728660094081</v>
       </c>
       <c r="C7">
-        <v>149.459692185814</v>
+        <v>147.9827275442667</v>
       </c>
       <c r="D7">
-        <v>136.059692185814</v>
+        <v>136.1427275442667</v>
       </c>
       <c r="E7">
-        <v>-8.800000000000001</v>
+        <v>-7.24</v>
       </c>
       <c r="F7">
-        <v>7.800000000000001</v>
+        <v>9.360000000000001</v>
       </c>
       <c r="G7">
         <v>21.2</v>
@@ -1983,28 +1983,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M7">
-        <v>0.39234</v>
+        <v>0.4708080000000001</v>
       </c>
       <c r="N7">
-        <v>10.16877111111111</v>
+        <v>10.09030311111111</v>
       </c>
       <c r="O7">
-        <v>1.016877111111111</v>
+        <v>1.009030311111111</v>
       </c>
       <c r="P7">
-        <v>9.151893999999999</v>
+        <v>9.081272799999999</v>
       </c>
       <c r="Q7">
-        <v>10.701894</v>
+        <v>10.6312728</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0875673315344023</v>
+        <v>0.08796924106483064</v>
       </c>
       <c r="T7">
-        <v>0.8371701914319025</v>
+        <v>0.8452259294014173</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.91826250474361</v>
+        <v>22.43188542061968</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08540728660094081</v>
+        <v>0.08536210824419942</v>
       </c>
       <c r="C8">
-        <v>147.9827275442667</v>
+        <v>146.5058643152842</v>
       </c>
       <c r="D8">
-        <v>136.1427275442667</v>
+        <v>136.2258643152842</v>
       </c>
       <c r="E8">
-        <v>-7.240000000000002</v>
+        <v>-5.680000000000003</v>
       </c>
       <c r="F8">
-        <v>9.359999999999999</v>
+        <v>10.92</v>
       </c>
       <c r="G8">
         <v>21.2</v>
@@ -2065,28 +2065,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M8">
-        <v>0.4708079999999999</v>
+        <v>0.5492759999999999</v>
       </c>
       <c r="N8">
-        <v>10.09030311111111</v>
+        <v>10.01183511111111</v>
       </c>
       <c r="O8">
-        <v>1.009030311111111</v>
+        <v>1.001183511111111</v>
       </c>
       <c r="P8">
-        <v>9.081272799999999</v>
+        <v>9.010651599999999</v>
       </c>
       <c r="Q8">
-        <v>10.6312728</v>
+        <v>10.5606516</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08796924106483064</v>
+        <v>0.08837979381096711</v>
       </c>
       <c r="T8">
-        <v>0.8452259294014173</v>
+        <v>0.8534549090476957</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.43188542061968</v>
+        <v>19.22733036053116</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08536210824419942</v>
+        <v>0.08531692988745804</v>
       </c>
       <c r="C9">
-        <v>146.5058643152842</v>
+        <v>145.0291026847653</v>
       </c>
       <c r="D9">
-        <v>136.2258643152842</v>
+        <v>136.3091026847653</v>
       </c>
       <c r="E9">
-        <v>-5.68</v>
+        <v>-4.120000000000001</v>
       </c>
       <c r="F9">
-        <v>10.92</v>
+        <v>12.48</v>
       </c>
       <c r="G9">
         <v>21.2</v>
@@ -2147,28 +2147,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M9">
-        <v>0.5492760000000001</v>
+        <v>0.627744</v>
       </c>
       <c r="N9">
-        <v>10.01183511111111</v>
+        <v>9.93336711111111</v>
       </c>
       <c r="O9">
-        <v>1.001183511111111</v>
+        <v>0.9933367111111111</v>
       </c>
       <c r="P9">
-        <v>9.010651599999999</v>
+        <v>8.940030399999999</v>
       </c>
       <c r="Q9">
-        <v>10.5606516</v>
+        <v>10.4900304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08837979381096711</v>
+        <v>0.08879927161680221</v>
       </c>
       <c r="T9">
-        <v>0.8534549090476958</v>
+        <v>0.8618627795558499</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.22733036053115</v>
+        <v>16.82391406546476</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08531692988745804</v>
+        <v>0.08527175153071663</v>
       </c>
       <c r="C10">
-        <v>145.0291026847653</v>
+        <v>143.5524428390637</v>
       </c>
       <c r="D10">
-        <v>136.3091026847653</v>
+        <v>136.3924428390637</v>
       </c>
       <c r="E10">
-        <v>-4.120000000000001</v>
+        <v>-2.560000000000002</v>
       </c>
       <c r="F10">
-        <v>12.48</v>
+        <v>14.04</v>
       </c>
       <c r="G10">
         <v>21.2</v>
@@ -2229,28 +2229,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M10">
-        <v>0.627744</v>
+        <v>0.706212</v>
       </c>
       <c r="N10">
-        <v>9.93336711111111</v>
+        <v>9.854899111111109</v>
       </c>
       <c r="O10">
-        <v>0.9933367111111111</v>
+        <v>0.9854899111111109</v>
       </c>
       <c r="P10">
-        <v>8.940030399999999</v>
+        <v>8.869409199999998</v>
       </c>
       <c r="Q10">
-        <v>10.4900304</v>
+        <v>10.4194092</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08879927161680221</v>
+        <v>0.08922796871507321</v>
       </c>
       <c r="T10">
-        <v>0.8618627795558499</v>
+        <v>0.8704554384268205</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.82391406546476</v>
+        <v>14.95459028041312</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08527175153071663</v>
+        <v>0.08522657317397525</v>
       </c>
       <c r="C11">
-        <v>143.5524428390637</v>
+        <v>142.075884964989</v>
       </c>
       <c r="D11">
-        <v>136.3924428390637</v>
+        <v>136.475884964989</v>
       </c>
       <c r="E11">
-        <v>-2.560000000000002</v>
+        <v>-1.000000000000004</v>
       </c>
       <c r="F11">
-        <v>14.04</v>
+        <v>15.6</v>
       </c>
       <c r="G11">
         <v>21.2</v>
@@ -2311,28 +2311,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M11">
-        <v>0.706212</v>
+        <v>0.7846799999999998</v>
       </c>
       <c r="N11">
-        <v>9.854899111111109</v>
+        <v>9.77643111111111</v>
       </c>
       <c r="O11">
-        <v>0.9854899111111109</v>
+        <v>0.977643111111111</v>
       </c>
       <c r="P11">
-        <v>8.869409199999998</v>
+        <v>8.798787999999998</v>
       </c>
       <c r="Q11">
-        <v>10.4194092</v>
+        <v>10.348788</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08922796871507321</v>
+        <v>0.08966619241552805</v>
       </c>
       <c r="T11">
-        <v>0.8704554384268205</v>
+        <v>0.8792390452727017</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2349,7 +2349,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.95459028041312</v>
+        <v>13.45913125237181</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08522657317397525</v>
+        <v>0.08532989481723385</v>
       </c>
       <c r="C12">
-        <v>142.075884964989</v>
+        <v>140.3252051862616</v>
       </c>
       <c r="D12">
-        <v>136.475884964989</v>
+        <v>136.2852051862616</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>0.5599999999999987</v>
       </c>
       <c r="F12">
-        <v>15.6</v>
+        <v>17.16</v>
       </c>
       <c r="G12">
         <v>21.2</v>
@@ -2393,45 +2393,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M12">
-        <v>0.78468</v>
+        <v>0.888888</v>
       </c>
       <c r="N12">
-        <v>9.77643111111111</v>
+        <v>9.67222311111111</v>
       </c>
       <c r="O12">
-        <v>0.977643111111111</v>
+        <v>0.9672223111111111</v>
       </c>
       <c r="P12">
-        <v>8.798787999999998</v>
+        <v>8.705000799999999</v>
       </c>
       <c r="Q12">
-        <v>10.348788</v>
+        <v>10.2550008</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08966619241552805</v>
+        <v>0.09011426383958859</v>
       </c>
       <c r="T12">
-        <v>0.8792390452727017</v>
+        <v>0.8882200365420857</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.45913125237181</v>
+        <v>11.88126188126188</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08532989481723385</v>
+        <v>0.08529821646049247</v>
       </c>
       <c r="C13">
-        <v>140.3252051862616</v>
+        <v>138.8236108349832</v>
       </c>
       <c r="D13">
-        <v>136.2852051862616</v>
+        <v>136.3436108349832</v>
       </c>
       <c r="E13">
-        <v>0.5599999999999987</v>
+        <v>2.119999999999997</v>
       </c>
       <c r="F13">
-        <v>17.16</v>
+        <v>18.72</v>
       </c>
       <c r="G13">
         <v>21.2</v>
@@ -2475,28 +2475,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M13">
-        <v>0.888888</v>
+        <v>0.9696959999999999</v>
       </c>
       <c r="N13">
-        <v>9.67222311111111</v>
+        <v>9.591415111111111</v>
       </c>
       <c r="O13">
-        <v>0.9672223111111111</v>
+        <v>0.9591415111111111</v>
       </c>
       <c r="P13">
-        <v>8.705000799999999</v>
+        <v>8.6322736</v>
       </c>
       <c r="Q13">
-        <v>10.2550008</v>
+        <v>10.1822736</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09011426383958859</v>
+        <v>0.09057251870510508</v>
       </c>
       <c r="T13">
-        <v>0.8882200365420857</v>
+        <v>0.8974051412494104</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.88126188126188</v>
+        <v>10.89115672449006</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08529821646049247</v>
+        <v>0.08526653810375108</v>
       </c>
       <c r="C14">
-        <v>138.8236108349832</v>
+        <v>137.3220665651838</v>
       </c>
       <c r="D14">
-        <v>136.3436108349832</v>
+        <v>136.4020665651838</v>
       </c>
       <c r="E14">
-        <v>2.119999999999997</v>
+        <v>3.68</v>
       </c>
       <c r="F14">
-        <v>18.72</v>
+        <v>20.28</v>
       </c>
       <c r="G14">
         <v>21.2</v>
@@ -2557,28 +2557,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M14">
-        <v>0.9696959999999999</v>
+        <v>1.050504</v>
       </c>
       <c r="N14">
-        <v>9.591415111111111</v>
+        <v>9.51060711111111</v>
       </c>
       <c r="O14">
-        <v>0.9591415111111111</v>
+        <v>0.951060711111111</v>
       </c>
       <c r="P14">
-        <v>8.6322736</v>
+        <v>8.559546399999999</v>
       </c>
       <c r="Q14">
-        <v>10.1822736</v>
+        <v>10.1095464</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09057251870510508</v>
+        <v>0.09104130816523112</v>
       </c>
       <c r="T14">
-        <v>0.8974051412494104</v>
+        <v>0.9068013977890873</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2595,7 +2595,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.89115672449006</v>
+        <v>10.05337543799082</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08526653810375108</v>
+        <v>0.08544905974700968</v>
       </c>
       <c r="C15">
-        <v>137.3220665651838</v>
+        <v>135.4259472478676</v>
       </c>
       <c r="D15">
-        <v>136.4020665651838</v>
+        <v>136.0659472478676</v>
       </c>
       <c r="E15">
-        <v>3.68</v>
+        <v>5.240000000000002</v>
       </c>
       <c r="F15">
-        <v>20.28</v>
+        <v>21.84</v>
       </c>
       <c r="G15">
         <v>21.2</v>
@@ -2639,45 +2639,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M15">
-        <v>1.050504</v>
+        <v>1.16844</v>
       </c>
       <c r="N15">
-        <v>9.51060711111111</v>
+        <v>9.39267111111111</v>
       </c>
       <c r="O15">
-        <v>0.951060711111111</v>
+        <v>0.9392671111111111</v>
       </c>
       <c r="P15">
-        <v>8.559546399999999</v>
+        <v>8.453403999999999</v>
       </c>
       <c r="Q15">
-        <v>10.1095464</v>
+        <v>10.003404</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09104130816523112</v>
+        <v>0.09152099970582522</v>
       </c>
       <c r="T15">
-        <v>0.9068013977890873</v>
+        <v>0.9164161719227102</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.05337543799082</v>
+        <v>9.038642216212308</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08544905974700968</v>
+        <v>0.0854326813902683</v>
       </c>
       <c r="C16">
-        <v>135.4259472478676</v>
+        <v>133.8960408358195</v>
       </c>
       <c r="D16">
-        <v>136.0659472478676</v>
+        <v>136.0960408358195</v>
       </c>
       <c r="E16">
-        <v>5.240000000000002</v>
+        <v>6.800000000000001</v>
       </c>
       <c r="F16">
-        <v>21.84</v>
+        <v>23.4</v>
       </c>
       <c r="G16">
         <v>21.2</v>
@@ -2721,28 +2721,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M16">
-        <v>1.16844</v>
+        <v>1.2519</v>
       </c>
       <c r="N16">
-        <v>9.39267111111111</v>
+        <v>9.309211111111111</v>
       </c>
       <c r="O16">
-        <v>0.9392671111111111</v>
+        <v>0.9309211111111111</v>
       </c>
       <c r="P16">
-        <v>8.453403999999999</v>
+        <v>8.37829</v>
       </c>
       <c r="Q16">
-        <v>10.003404</v>
+        <v>9.928290000000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09152099970582522</v>
+        <v>0.09201197810619799</v>
       </c>
       <c r="T16">
-        <v>0.9164161719227102</v>
+        <v>0.9262571760359478</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.038642216212308</v>
+        <v>8.436066068464822</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0854326813902683</v>
+        <v>0.08541630303352692</v>
       </c>
       <c r="C17">
-        <v>133.8960408358195</v>
+        <v>132.3661477382618</v>
       </c>
       <c r="D17">
-        <v>136.0960408358195</v>
+        <v>136.1261477382619</v>
       </c>
       <c r="E17">
-        <v>6.799999999999997</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="F17">
-        <v>23.4</v>
+        <v>24.96</v>
       </c>
       <c r="G17">
         <v>21.2</v>
@@ -2803,28 +2803,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M17">
-        <v>1.2519</v>
+        <v>1.33536</v>
       </c>
       <c r="N17">
-        <v>9.309211111111111</v>
+        <v>9.22575111111111</v>
       </c>
       <c r="O17">
-        <v>0.9309211111111111</v>
+        <v>0.9225751111111111</v>
       </c>
       <c r="P17">
-        <v>8.37829</v>
+        <v>8.303175999999999</v>
       </c>
       <c r="Q17">
-        <v>9.928290000000001</v>
+        <v>9.853175999999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09201197810619799</v>
+        <v>0.09251464646848442</v>
       </c>
       <c r="T17">
-        <v>0.9262571760359478</v>
+        <v>0.9363324897709291</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.436066068464823</v>
+        <v>7.90881193918577</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08541630303352692</v>
+        <v>0.08552232467678551</v>
       </c>
       <c r="C18">
-        <v>132.3661477382618</v>
+        <v>130.6114930465306</v>
       </c>
       <c r="D18">
-        <v>136.1261477382619</v>
+        <v>135.9314930465306</v>
       </c>
       <c r="E18">
-        <v>8.359999999999999</v>
+        <v>9.920000000000002</v>
       </c>
       <c r="F18">
-        <v>24.96</v>
+        <v>26.52</v>
       </c>
       <c r="G18">
         <v>21.2</v>
@@ -2885,45 +2885,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M18">
-        <v>1.33536</v>
+        <v>1.440036</v>
       </c>
       <c r="N18">
-        <v>9.22575111111111</v>
+        <v>9.121075111111111</v>
       </c>
       <c r="O18">
-        <v>0.9225751111111111</v>
+        <v>0.9121075111111111</v>
       </c>
       <c r="P18">
-        <v>8.303175999999999</v>
+        <v>8.208967599999999</v>
       </c>
       <c r="Q18">
-        <v>9.853175999999999</v>
+        <v>9.7589676</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09251464646848442</v>
+        <v>0.09302942732142833</v>
       </c>
       <c r="T18">
-        <v>0.9363324897709291</v>
+        <v>0.9466505821501268</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.90881193918577</v>
+        <v>7.333921590231848</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08552232467678551</v>
+        <v>0.08551314632004411</v>
       </c>
       <c r="C19">
-        <v>130.6114930465306</v>
+        <v>129.0683224056047</v>
       </c>
       <c r="D19">
-        <v>135.9314930465306</v>
+        <v>135.9483224056047</v>
       </c>
       <c r="E19">
-        <v>9.920000000000002</v>
+        <v>11.48</v>
       </c>
       <c r="F19">
-        <v>26.52</v>
+        <v>28.08</v>
       </c>
       <c r="G19">
         <v>21.2</v>
@@ -2967,28 +2967,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M19">
-        <v>1.440036</v>
+        <v>1.524744</v>
       </c>
       <c r="N19">
-        <v>9.121075111111111</v>
+        <v>9.03636711111111</v>
       </c>
       <c r="O19">
-        <v>0.9121075111111111</v>
+        <v>0.903636711111111</v>
       </c>
       <c r="P19">
-        <v>8.208967599999999</v>
+        <v>8.1327304</v>
       </c>
       <c r="Q19">
-        <v>9.7589676</v>
+        <v>9.682730400000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09302942732142833</v>
+        <v>0.09355676380493186</v>
       </c>
       <c r="T19">
-        <v>0.9466505821501268</v>
+        <v>0.957220335319061</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.333921590231848</v>
+        <v>6.926481501885634</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08551314632004413</v>
+        <v>0.08550396796330274</v>
       </c>
       <c r="C20">
-        <v>129.0683224056047</v>
+        <v>127.5251559324016</v>
       </c>
       <c r="D20">
-        <v>135.9483224056047</v>
+        <v>135.9651559324016</v>
       </c>
       <c r="E20">
-        <v>11.48</v>
+        <v>13.04</v>
       </c>
       <c r="F20">
-        <v>28.08</v>
+        <v>29.64</v>
       </c>
       <c r="G20">
         <v>21.2</v>
@@ -3049,28 +3049,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M20">
-        <v>1.524744</v>
+        <v>1.609452</v>
       </c>
       <c r="N20">
-        <v>9.03636711111111</v>
+        <v>8.951659111111109</v>
       </c>
       <c r="O20">
-        <v>0.903636711111111</v>
+        <v>0.895165911111111</v>
       </c>
       <c r="P20">
-        <v>8.1327304</v>
+        <v>8.056493199999998</v>
       </c>
       <c r="Q20">
-        <v>9.682730400000001</v>
+        <v>9.606493199999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09355676380493186</v>
+        <v>0.09409712094234907</v>
       </c>
       <c r="T20">
-        <v>0.957220335319061</v>
+        <v>0.968051070047722</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.926481501885635</v>
+        <v>6.561929843891653</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08550396796330274</v>
+        <v>0.08549478960656137</v>
       </c>
       <c r="C21">
-        <v>127.5251559324016</v>
+        <v>125.9819936284699</v>
       </c>
       <c r="D21">
-        <v>135.9651559324016</v>
+        <v>135.9819936284699</v>
       </c>
       <c r="E21">
-        <v>13.04</v>
+        <v>14.6</v>
       </c>
       <c r="F21">
-        <v>29.64</v>
+        <v>31.2</v>
       </c>
       <c r="G21">
         <v>21.2</v>
@@ -3131,28 +3131,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M21">
-        <v>1.609452</v>
+        <v>1.69416</v>
       </c>
       <c r="N21">
-        <v>8.951659111111109</v>
+        <v>8.86695111111111</v>
       </c>
       <c r="O21">
-        <v>0.895165911111111</v>
+        <v>0.886695111111111</v>
       </c>
       <c r="P21">
-        <v>8.056493199999998</v>
+        <v>7.980255999999999</v>
       </c>
       <c r="Q21">
-        <v>9.606493199999999</v>
+        <v>9.530256</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09409712094234907</v>
+        <v>0.0946509870082017</v>
       </c>
       <c r="T21">
-        <v>0.968051070047722</v>
+        <v>0.9791525731445997</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.561929843891653</v>
+        <v>6.23383335169707</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08549478960656137</v>
+        <v>0.08567461124981998</v>
       </c>
       <c r="C22">
-        <v>125.9819936284699</v>
+        <v>124.0928684929745</v>
       </c>
       <c r="D22">
-        <v>135.9819936284699</v>
+        <v>135.6528684929745</v>
       </c>
       <c r="E22">
-        <v>14.6</v>
+        <v>16.16</v>
       </c>
       <c r="F22">
-        <v>31.2</v>
+        <v>32.76000000000001</v>
       </c>
       <c r="G22">
         <v>21.2</v>
@@ -3213,45 +3213,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M22">
-        <v>1.69416</v>
+        <v>1.811628</v>
       </c>
       <c r="N22">
-        <v>8.86695111111111</v>
+        <v>8.749483111111109</v>
       </c>
       <c r="O22">
-        <v>0.886695111111111</v>
+        <v>0.8749483111111109</v>
       </c>
       <c r="P22">
-        <v>7.980255999999999</v>
+        <v>7.874534799999998</v>
       </c>
       <c r="Q22">
-        <v>9.530256</v>
+        <v>9.424534799999998</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0946509870082017</v>
+        <v>0.09521887499977211</v>
       </c>
       <c r="T22">
-        <v>0.9791525731445997</v>
+        <v>0.9905351269527904</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.23383335169707</v>
+        <v>5.829624575857244</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08567461124981997</v>
+        <v>0.08567443289307858</v>
       </c>
       <c r="C23">
-        <v>124.0928684929745</v>
+        <v>122.5331941475903</v>
       </c>
       <c r="D23">
-        <v>135.6528684929745</v>
+        <v>135.6531941475903</v>
       </c>
       <c r="E23">
-        <v>16.16</v>
+        <v>17.72</v>
       </c>
       <c r="F23">
-        <v>32.76</v>
+        <v>34.32</v>
       </c>
       <c r="G23">
         <v>21.2</v>
@@ -3295,28 +3295,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M23">
-        <v>1.811628</v>
+        <v>1.897896</v>
       </c>
       <c r="N23">
-        <v>8.749483111111109</v>
+        <v>8.663215111111111</v>
       </c>
       <c r="O23">
-        <v>0.8749483111111109</v>
+        <v>0.8663215111111111</v>
       </c>
       <c r="P23">
-        <v>7.874534799999998</v>
+        <v>7.7968936</v>
       </c>
       <c r="Q23">
-        <v>9.424534799999998</v>
+        <v>9.3468936</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09521887499977211</v>
+        <v>0.09580132422189561</v>
       </c>
       <c r="T23">
-        <v>0.9905351269527904</v>
+        <v>1.002209541115038</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.829624575857245</v>
+        <v>5.564641640591008</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08567443289307858</v>
+        <v>0.08567425453633719</v>
       </c>
       <c r="C24">
-        <v>122.5331941475903</v>
+        <v>120.9735198037697</v>
       </c>
       <c r="D24">
-        <v>135.6531941475903</v>
+        <v>135.6535198037697</v>
       </c>
       <c r="E24">
-        <v>17.72</v>
+        <v>19.28</v>
       </c>
       <c r="F24">
-        <v>34.32</v>
+        <v>35.88</v>
       </c>
       <c r="G24">
         <v>21.2</v>
@@ -3377,28 +3377,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M24">
-        <v>1.897896</v>
+        <v>1.984164</v>
       </c>
       <c r="N24">
-        <v>8.663215111111111</v>
+        <v>8.57694711111111</v>
       </c>
       <c r="O24">
-        <v>0.8663215111111111</v>
+        <v>0.8576947111111111</v>
       </c>
       <c r="P24">
-        <v>7.7968936</v>
+        <v>7.719252399999999</v>
       </c>
       <c r="Q24">
-        <v>9.3468936</v>
+        <v>9.269252399999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09580132422189561</v>
+        <v>0.09639890199524309</v>
       </c>
       <c r="T24">
-        <v>1.002209541115038</v>
+        <v>1.014187186813966</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.564641640591008</v>
+        <v>5.322700699695745</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08567425453633719</v>
+        <v>0.0856740761795958</v>
       </c>
       <c r="C25">
-        <v>120.9735198037697</v>
+        <v>119.4138454615126</v>
       </c>
       <c r="D25">
-        <v>135.6535198037697</v>
+        <v>135.6538454615126</v>
       </c>
       <c r="E25">
-        <v>19.28</v>
+        <v>20.84</v>
       </c>
       <c r="F25">
-        <v>35.88</v>
+        <v>37.44</v>
       </c>
       <c r="G25">
         <v>21.2</v>
@@ -3459,28 +3459,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M25">
-        <v>1.984164</v>
+        <v>2.070432</v>
       </c>
       <c r="N25">
-        <v>8.57694711111111</v>
+        <v>8.49067911111111</v>
       </c>
       <c r="O25">
-        <v>0.8576947111111111</v>
+        <v>0.849067911111111</v>
       </c>
       <c r="P25">
-        <v>7.719252399999999</v>
+        <v>7.641611199999999</v>
       </c>
       <c r="Q25">
-        <v>9.269252399999999</v>
+        <v>9.191611199999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09639890199524309</v>
+        <v>0.09701220549946815</v>
       </c>
       <c r="T25">
-        <v>1.014187186813966</v>
+        <v>1.026480033715499</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.322700699695745</v>
+        <v>5.100921503875089</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0856740761795958</v>
+        <v>0.08567389782285439</v>
       </c>
       <c r="C26">
-        <v>119.4138454615126</v>
+        <v>117.8541711208192</v>
       </c>
       <c r="D26">
-        <v>135.6538454615126</v>
+        <v>135.6541711208192</v>
       </c>
       <c r="E26">
-        <v>20.84</v>
+        <v>22.4</v>
       </c>
       <c r="F26">
-        <v>37.44</v>
+        <v>39</v>
       </c>
       <c r="G26">
         <v>21.2</v>
@@ -3541,28 +3541,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M26">
-        <v>2.070432</v>
+        <v>2.1567</v>
       </c>
       <c r="N26">
-        <v>8.49067911111111</v>
+        <v>8.404411111111109</v>
       </c>
       <c r="O26">
-        <v>0.849067911111111</v>
+        <v>0.840441111111111</v>
       </c>
       <c r="P26">
-        <v>7.641611199999999</v>
+        <v>7.563969999999999</v>
       </c>
       <c r="Q26">
-        <v>9.191611199999999</v>
+        <v>9.113969999999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09701220549946815</v>
+        <v>0.09764186376380588</v>
       </c>
       <c r="T26">
-        <v>1.026480033715499</v>
+        <v>1.039100689867738</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.10092150387509</v>
+        <v>4.896884643720085</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08567389782285439</v>
+        <v>0.08567371946611302</v>
       </c>
       <c r="C27">
-        <v>117.8541711208192</v>
+        <v>116.2944967816893</v>
       </c>
       <c r="D27">
-        <v>135.6541711208192</v>
+        <v>135.6544967816893</v>
       </c>
       <c r="E27">
-        <v>22.4</v>
+        <v>23.96</v>
       </c>
       <c r="F27">
-        <v>39</v>
+        <v>40.56</v>
       </c>
       <c r="G27">
         <v>21.2</v>
@@ -3623,28 +3623,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M27">
-        <v>2.1567</v>
+        <v>2.242968</v>
       </c>
       <c r="N27">
-        <v>8.404411111111109</v>
+        <v>8.318143111111109</v>
       </c>
       <c r="O27">
-        <v>0.840441111111111</v>
+        <v>0.8318143111111109</v>
       </c>
       <c r="P27">
-        <v>7.563969999999999</v>
+        <v>7.486328799999998</v>
       </c>
       <c r="Q27">
-        <v>9.113969999999998</v>
+        <v>9.036328799999998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09764186376380588</v>
+        <v>0.09828853981907165</v>
       </c>
       <c r="T27">
-        <v>1.039100689867738</v>
+        <v>1.052062444834904</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.896884643720085</v>
+        <v>4.708542926653928</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08567371946611302</v>
+        <v>0.08567354110937163</v>
       </c>
       <c r="C28">
-        <v>116.2944967816893</v>
+        <v>114.734822444123</v>
       </c>
       <c r="D28">
-        <v>135.6544967816893</v>
+        <v>135.6548224441231</v>
       </c>
       <c r="E28">
-        <v>23.96</v>
+        <v>25.52</v>
       </c>
       <c r="F28">
-        <v>40.56</v>
+        <v>42.12</v>
       </c>
       <c r="G28">
         <v>21.2</v>
@@ -3705,28 +3705,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M28">
-        <v>2.242968</v>
+        <v>2.329236</v>
       </c>
       <c r="N28">
-        <v>8.318143111111109</v>
+        <v>8.23187511111111</v>
       </c>
       <c r="O28">
-        <v>0.8318143111111109</v>
+        <v>0.8231875111111111</v>
       </c>
       <c r="P28">
-        <v>7.486328799999998</v>
+        <v>7.408687599999999</v>
       </c>
       <c r="Q28">
-        <v>9.036328799999998</v>
+        <v>8.958687599999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09828853981907165</v>
+        <v>0.09895293302653647</v>
       </c>
       <c r="T28">
-        <v>1.052062444834904</v>
+        <v>1.065379316376512</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.708542926653928</v>
+        <v>4.534152447888968</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08567354110937163</v>
+        <v>0.08630336275263023</v>
       </c>
       <c r="C29">
-        <v>114.734822444123</v>
+        <v>112.034492318232</v>
       </c>
       <c r="D29">
-        <v>135.6548224441231</v>
+        <v>134.514492318232</v>
       </c>
       <c r="E29">
-        <v>25.52</v>
+        <v>27.08000000000001</v>
       </c>
       <c r="F29">
-        <v>42.12</v>
+        <v>43.68000000000001</v>
       </c>
       <c r="G29">
         <v>21.2</v>
@@ -3787,45 +3787,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M29">
-        <v>2.329236</v>
+        <v>2.524704000000001</v>
       </c>
       <c r="N29">
-        <v>8.23187511111111</v>
+        <v>8.03640711111111</v>
       </c>
       <c r="O29">
-        <v>0.8231875111111111</v>
+        <v>0.803640711111111</v>
       </c>
       <c r="P29">
-        <v>7.408687599999999</v>
+        <v>7.232766399999999</v>
       </c>
       <c r="Q29">
-        <v>8.958687599999999</v>
+        <v>8.7827664</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09895293302653647</v>
+        <v>0.09963578160087533</v>
       </c>
       <c r="T29">
-        <v>1.065379316376512</v>
+        <v>1.079066101016497</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.1</v>
       </c>
       <c r="W29">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.534152447888968</v>
+        <v>4.183108638125938</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08630336275263023</v>
+        <v>0.08632568439588886</v>
       </c>
       <c r="C30">
-        <v>112.034492318232</v>
+        <v>110.434429301095</v>
       </c>
       <c r="D30">
-        <v>134.514492318232</v>
+        <v>134.474429301095</v>
       </c>
       <c r="E30">
-        <v>27.08000000000001</v>
+        <v>28.64000000000001</v>
       </c>
       <c r="F30">
-        <v>43.68000000000001</v>
+        <v>45.24000000000001</v>
       </c>
       <c r="G30">
         <v>21.2</v>
@@ -3869,28 +3869,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M30">
-        <v>2.524704000000001</v>
+        <v>2.614872000000001</v>
       </c>
       <c r="N30">
-        <v>8.03640711111111</v>
+        <v>7.94623911111111</v>
       </c>
       <c r="O30">
-        <v>0.803640711111111</v>
+        <v>0.7946239111111111</v>
       </c>
       <c r="P30">
-        <v>7.232766399999999</v>
+        <v>7.151615199999998</v>
       </c>
       <c r="Q30">
-        <v>8.7827664</v>
+        <v>8.701615199999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09963578160087533</v>
+        <v>0.1003378653463223</v>
       </c>
       <c r="T30">
-        <v>1.079066101016497</v>
+        <v>1.093138428885779</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.183108638125938</v>
+        <v>4.03886351267332</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08632568439588884</v>
+        <v>0.08729300603914744</v>
       </c>
       <c r="C31">
-        <v>110.434429301095</v>
+        <v>107.1609079051675</v>
       </c>
       <c r="D31">
-        <v>134.474429301095</v>
+        <v>132.7609079051675</v>
       </c>
       <c r="E31">
-        <v>28.63999999999999</v>
+        <v>30.2</v>
       </c>
       <c r="F31">
-        <v>45.23999999999999</v>
+        <v>46.8</v>
       </c>
       <c r="G31">
         <v>21.2</v>
@@ -3951,45 +3951,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M31">
-        <v>2.614872</v>
+        <v>2.86884</v>
       </c>
       <c r="N31">
-        <v>7.94623911111111</v>
+        <v>7.69227111111111</v>
       </c>
       <c r="O31">
-        <v>0.7946239111111111</v>
+        <v>0.769227111111111</v>
       </c>
       <c r="P31">
-        <v>7.151615199999998</v>
+        <v>6.923043999999998</v>
       </c>
       <c r="Q31">
-        <v>8.701615199999999</v>
+        <v>8.473043999999998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1003378653463223</v>
+        <v>0.1010600086273535</v>
       </c>
       <c r="T31">
-        <v>1.093138428885779</v>
+        <v>1.107612823265611</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.1</v>
       </c>
       <c r="W31">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.03886351267332</v>
+        <v>3.681317574737911</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08729300603914744</v>
+        <v>0.08734682768240608</v>
       </c>
       <c r="C32">
-        <v>107.1609079051675</v>
+        <v>105.5068493538426</v>
       </c>
       <c r="D32">
-        <v>132.7609079051675</v>
+        <v>132.6668493538426</v>
       </c>
       <c r="E32">
-        <v>30.2</v>
+        <v>31.76</v>
       </c>
       <c r="F32">
-        <v>46.8</v>
+        <v>48.36</v>
       </c>
       <c r="G32">
         <v>21.2</v>
@@ -4033,28 +4033,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M32">
-        <v>2.86884</v>
+        <v>2.964468</v>
       </c>
       <c r="N32">
-        <v>7.69227111111111</v>
+        <v>7.59664311111111</v>
       </c>
       <c r="O32">
-        <v>0.769227111111111</v>
+        <v>0.759664311111111</v>
       </c>
       <c r="P32">
-        <v>6.923043999999998</v>
+        <v>6.836978799999999</v>
       </c>
       <c r="Q32">
-        <v>8.473043999999998</v>
+        <v>8.3869788</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1010600086273535</v>
+        <v>0.10180308359769</v>
       </c>
       <c r="T32">
-        <v>1.107612823265611</v>
+        <v>1.122506765308627</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.681317574737911</v>
+        <v>3.562565394907656</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08734682768240608</v>
+        <v>0.08820704932566467</v>
       </c>
       <c r="C33">
-        <v>105.5068493538426</v>
+        <v>102.4614138799199</v>
       </c>
       <c r="D33">
-        <v>132.6668493538426</v>
+        <v>131.1814138799199</v>
       </c>
       <c r="E33">
-        <v>31.76</v>
+        <v>33.32</v>
       </c>
       <c r="F33">
-        <v>48.36</v>
+        <v>49.92</v>
       </c>
       <c r="G33">
         <v>21.2</v>
@@ -4115,45 +4115,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M33">
-        <v>2.964468</v>
+        <v>3.199872</v>
       </c>
       <c r="N33">
-        <v>7.59664311111111</v>
+        <v>7.361239111111109</v>
       </c>
       <c r="O33">
-        <v>0.759664311111111</v>
+        <v>0.736123911111111</v>
       </c>
       <c r="P33">
-        <v>6.836978799999999</v>
+        <v>6.625115199999998</v>
       </c>
       <c r="Q33">
-        <v>8.3869788</v>
+        <v>8.175115199999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.10180308359769</v>
+        <v>0.1025680137142128</v>
       </c>
       <c r="T33">
-        <v>1.122506765308627</v>
+        <v>1.137838764470555</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.1</v>
       </c>
       <c r="W33">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.562565394907656</v>
+        <v>3.300479241391877</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08820704932566467</v>
+        <v>0.08828607096892328</v>
       </c>
       <c r="C34">
-        <v>102.4614138799199</v>
+        <v>100.7666253586384</v>
       </c>
       <c r="D34">
-        <v>131.1814138799199</v>
+        <v>131.0466253586384</v>
       </c>
       <c r="E34">
-        <v>33.32</v>
+        <v>34.88</v>
       </c>
       <c r="F34">
-        <v>49.92</v>
+        <v>51.48</v>
       </c>
       <c r="G34">
         <v>21.2</v>
@@ -4197,28 +4197,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M34">
-        <v>3.199872</v>
+        <v>3.299868</v>
       </c>
       <c r="N34">
-        <v>7.361239111111109</v>
+        <v>7.26124311111111</v>
       </c>
       <c r="O34">
-        <v>0.736123911111111</v>
+        <v>0.7261243111111111</v>
       </c>
       <c r="P34">
-        <v>6.625115199999998</v>
+        <v>6.535118799999999</v>
       </c>
       <c r="Q34">
-        <v>8.175115199999999</v>
+        <v>8.0851188</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1025680137142128</v>
+        <v>0.1033557775655572</v>
       </c>
       <c r="T34">
-        <v>1.137838764470555</v>
+        <v>1.153628435249257</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.300479241391877</v>
+        <v>3.200464718925457</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08828607096892328</v>
+        <v>0.08836509261218189</v>
       </c>
       <c r="C35">
-        <v>100.7666253586384</v>
+        <v>99.07211354267032</v>
       </c>
       <c r="D35">
-        <v>131.0466253586384</v>
+        <v>130.9121135426703</v>
       </c>
       <c r="E35">
-        <v>34.88</v>
+        <v>36.44</v>
       </c>
       <c r="F35">
-        <v>51.48</v>
+        <v>53.04000000000001</v>
       </c>
       <c r="G35">
         <v>21.2</v>
@@ -4279,28 +4279,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M35">
-        <v>3.299868</v>
+        <v>3.399864</v>
       </c>
       <c r="N35">
-        <v>7.26124311111111</v>
+        <v>7.161247111111109</v>
       </c>
       <c r="O35">
-        <v>0.7261243111111111</v>
+        <v>0.716124711111111</v>
       </c>
       <c r="P35">
-        <v>6.535118799999999</v>
+        <v>6.445122399999998</v>
       </c>
       <c r="Q35">
-        <v>8.0851188</v>
+        <v>7.995122399999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1033557775655572</v>
+        <v>0.1041674130487605</v>
       </c>
       <c r="T35">
-        <v>1.153628435249257</v>
+        <v>1.169896580900041</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.200464718925457</v>
+        <v>3.106333403662943</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08836509261218189</v>
+        <v>0.08844411425544051</v>
       </c>
       <c r="C36">
-        <v>99.07211354267032</v>
+        <v>97.37787758082307</v>
       </c>
       <c r="D36">
-        <v>130.9121135426703</v>
+        <v>130.7778775808231</v>
       </c>
       <c r="E36">
-        <v>36.44</v>
+        <v>38.00000000000001</v>
       </c>
       <c r="F36">
-        <v>53.04000000000001</v>
+        <v>54.60000000000001</v>
       </c>
       <c r="G36">
         <v>21.2</v>
@@ -4361,28 +4361,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M36">
-        <v>3.399864</v>
+        <v>3.499860000000001</v>
       </c>
       <c r="N36">
-        <v>7.161247111111109</v>
+        <v>7.061251111111109</v>
       </c>
       <c r="O36">
-        <v>0.716124711111111</v>
+        <v>0.706125111111111</v>
       </c>
       <c r="P36">
-        <v>6.445122399999998</v>
+        <v>6.355125999999998</v>
       </c>
       <c r="Q36">
-        <v>7.995122399999998</v>
+        <v>7.905125999999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1041674130487605</v>
+        <v>0.105004021931447</v>
       </c>
       <c r="T36">
-        <v>1.169896580900041</v>
+        <v>1.186665284878542</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.106333403662943</v>
+        <v>3.017581020701145</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08844411425544051</v>
+        <v>0.09105033589869911</v>
       </c>
       <c r="C37">
-        <v>97.37787758082307</v>
+        <v>91.53984270781328</v>
       </c>
       <c r="D37">
-        <v>130.7778775808231</v>
+        <v>126.4998427078133</v>
       </c>
       <c r="E37">
-        <v>38.00000000000001</v>
+        <v>39.56</v>
       </c>
       <c r="F37">
-        <v>54.60000000000001</v>
+        <v>56.16</v>
       </c>
       <c r="G37">
         <v>21.2</v>
@@ -4443,45 +4443,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M37">
-        <v>3.499860000000001</v>
+        <v>4.037904</v>
       </c>
       <c r="N37">
-        <v>7.061251111111109</v>
+        <v>6.52320711111111</v>
       </c>
       <c r="O37">
-        <v>0.706125111111111</v>
+        <v>0.652320711111111</v>
       </c>
       <c r="P37">
-        <v>6.355125999999998</v>
+        <v>5.870886399999999</v>
       </c>
       <c r="Q37">
-        <v>7.905125999999998</v>
+        <v>7.420886399999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.105004021931447</v>
+        <v>0.1058667748417174</v>
       </c>
       <c r="T37">
-        <v>1.186665284878542</v>
+        <v>1.20395801085637</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.017581020701145</v>
+        <v>2.615493362673087</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09105033589869913</v>
+        <v>0.09119955754195773</v>
       </c>
       <c r="C38">
-        <v>91.53984270781325</v>
+        <v>89.74335540223964</v>
       </c>
       <c r="D38">
-        <v>126.4998427078132</v>
+        <v>126.2633554022397</v>
       </c>
       <c r="E38">
-        <v>39.56</v>
+        <v>41.12</v>
       </c>
       <c r="F38">
-        <v>56.16</v>
+        <v>57.72</v>
       </c>
       <c r="G38">
         <v>21.2</v>
@@ -4525,28 +4525,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M38">
-        <v>4.037904</v>
+        <v>4.150068</v>
       </c>
       <c r="N38">
-        <v>6.52320711111111</v>
+        <v>6.41104311111111</v>
       </c>
       <c r="O38">
-        <v>0.652320711111111</v>
+        <v>0.641104311111111</v>
       </c>
       <c r="P38">
-        <v>5.870886399999999</v>
+        <v>5.769938799999998</v>
       </c>
       <c r="Q38">
-        <v>7.420886399999999</v>
+        <v>7.319938799999998</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1058667748417174</v>
+        <v>0.1067569167332662</v>
       </c>
       <c r="T38">
-        <v>1.20395801085637</v>
+        <v>1.221799712262066</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.615493362673087</v>
+        <v>2.544804352871112</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09119955754195773</v>
+        <v>0.09268257918521636</v>
       </c>
       <c r="C39">
-        <v>89.74335540223964</v>
+        <v>85.88023881648857</v>
       </c>
       <c r="D39">
-        <v>126.2633554022397</v>
+        <v>123.9602388164886</v>
       </c>
       <c r="E39">
-        <v>41.12</v>
+        <v>42.68</v>
       </c>
       <c r="F39">
-        <v>57.72</v>
+        <v>59.28</v>
       </c>
       <c r="G39">
         <v>21.2</v>
@@ -4607,45 +4607,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M39">
-        <v>4.150068</v>
+        <v>4.493424</v>
       </c>
       <c r="N39">
-        <v>6.41104311111111</v>
+        <v>6.06768711111111</v>
       </c>
       <c r="O39">
-        <v>0.641104311111111</v>
+        <v>0.6067687111111111</v>
       </c>
       <c r="P39">
-        <v>5.769938799999998</v>
+        <v>5.460918399999999</v>
       </c>
       <c r="Q39">
-        <v>7.319938799999998</v>
+        <v>7.010918399999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1067569167332662</v>
+        <v>0.1076757728793812</v>
       </c>
       <c r="T39">
-        <v>1.221799712262066</v>
+        <v>1.240216952422785</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.1</v>
       </c>
       <c r="W39">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.544804352871112</v>
+        <v>2.350348222449319</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09268257918521636</v>
+        <v>0.09286690082847494</v>
       </c>
       <c r="C40">
-        <v>85.88023881648857</v>
+        <v>84.03984632615854</v>
       </c>
       <c r="D40">
-        <v>123.9602388164886</v>
+        <v>123.6798463261585</v>
       </c>
       <c r="E40">
-        <v>42.68</v>
+        <v>44.24</v>
       </c>
       <c r="F40">
-        <v>59.28</v>
+        <v>60.84</v>
       </c>
       <c r="G40">
         <v>21.2</v>
@@ -4689,28 +4689,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M40">
-        <v>4.493424</v>
+        <v>4.611672</v>
       </c>
       <c r="N40">
-        <v>6.06768711111111</v>
+        <v>5.94943911111111</v>
       </c>
       <c r="O40">
-        <v>0.6067687111111111</v>
+        <v>0.594943911111111</v>
       </c>
       <c r="P40">
-        <v>5.460918399999999</v>
+        <v>5.354495199999999</v>
       </c>
       <c r="Q40">
-        <v>7.010918399999999</v>
+        <v>6.904495199999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1076757728793812</v>
+        <v>0.1086247554565163</v>
       </c>
       <c r="T40">
-        <v>1.240216952422785</v>
+        <v>1.259238036523199</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.350348222449319</v>
+        <v>2.290082883412157</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09286690082847494</v>
+        <v>0.09305122247173357</v>
       </c>
       <c r="C41">
-        <v>84.03984632615854</v>
+        <v>82.20071944350937</v>
       </c>
       <c r="D41">
-        <v>123.6798463261585</v>
+        <v>123.4007194435094</v>
       </c>
       <c r="E41">
-        <v>44.24</v>
+        <v>45.8</v>
       </c>
       <c r="F41">
-        <v>60.84</v>
+        <v>62.40000000000001</v>
       </c>
       <c r="G41">
         <v>21.2</v>
@@ -4771,28 +4771,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M41">
-        <v>4.611672</v>
+        <v>4.729920000000001</v>
       </c>
       <c r="N41">
-        <v>5.94943911111111</v>
+        <v>5.831191111111109</v>
       </c>
       <c r="O41">
-        <v>0.594943911111111</v>
+        <v>0.5831191111111109</v>
       </c>
       <c r="P41">
-        <v>5.354495199999999</v>
+        <v>5.248071999999999</v>
       </c>
       <c r="Q41">
-        <v>6.904495199999999</v>
+        <v>6.798071999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1086247554565163</v>
+        <v>0.1096053707862226</v>
       </c>
       <c r="T41">
-        <v>1.259238036523199</v>
+        <v>1.278893156760293</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.290082883412157</v>
+        <v>2.232830811326853</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09305122247173357</v>
+        <v>0.09323554411499217</v>
       </c>
       <c r="C42">
-        <v>82.20071944350937</v>
+        <v>80.36284961897556</v>
       </c>
       <c r="D42">
-        <v>123.4007194435094</v>
+        <v>123.1228496189756</v>
       </c>
       <c r="E42">
-        <v>45.8</v>
+        <v>47.36000000000001</v>
       </c>
       <c r="F42">
-        <v>62.40000000000001</v>
+        <v>63.96000000000001</v>
       </c>
       <c r="G42">
         <v>21.2</v>
@@ -4853,28 +4853,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M42">
-        <v>4.729920000000001</v>
+        <v>4.848168000000001</v>
       </c>
       <c r="N42">
-        <v>5.831191111111109</v>
+        <v>5.712943111111109</v>
       </c>
       <c r="O42">
-        <v>0.5831191111111109</v>
+        <v>0.571294311111111</v>
       </c>
       <c r="P42">
-        <v>5.248071999999999</v>
+        <v>5.141648799999998</v>
       </c>
       <c r="Q42">
-        <v>6.798071999999999</v>
+        <v>6.691648799999998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1096053707862226</v>
+        <v>0.1106192273135461</v>
       </c>
       <c r="T42">
-        <v>1.278893156760293</v>
+        <v>1.299214552259662</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.232830811326853</v>
+        <v>2.17837152324571</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09323554411499217</v>
+        <v>0.0934198657582508</v>
       </c>
       <c r="C43">
-        <v>80.36284961897556</v>
+        <v>78.52622837982489</v>
       </c>
       <c r="D43">
-        <v>123.1228496189756</v>
+        <v>122.8462283798249</v>
       </c>
       <c r="E43">
-        <v>47.36000000000001</v>
+        <v>48.92000000000001</v>
       </c>
       <c r="F43">
-        <v>63.96000000000001</v>
+        <v>65.52000000000001</v>
       </c>
       <c r="G43">
         <v>21.2</v>
@@ -4935,28 +4935,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M43">
-        <v>4.848168000000001</v>
+        <v>4.966416000000001</v>
       </c>
       <c r="N43">
-        <v>5.712943111111109</v>
+        <v>5.594695111111109</v>
       </c>
       <c r="O43">
-        <v>0.571294311111111</v>
+        <v>0.5594695111111109</v>
       </c>
       <c r="P43">
-        <v>5.141648799999998</v>
+        <v>5.035225599999998</v>
       </c>
       <c r="Q43">
-        <v>6.691648799999998</v>
+        <v>6.585225599999998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1106192273135461</v>
+        <v>0.1116680444107772</v>
       </c>
       <c r="T43">
-        <v>1.299214552259662</v>
+        <v>1.320236685534872</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.17837152324571</v>
+        <v>2.126505534597003</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09341986575825079</v>
+        <v>0.0936041874015094</v>
       </c>
       <c r="C44">
-        <v>78.52622837982493</v>
+        <v>76.69084732929771</v>
       </c>
       <c r="D44">
-        <v>122.8462283798249</v>
+        <v>122.5708473292977</v>
       </c>
       <c r="E44">
-        <v>48.91999999999999</v>
+        <v>50.48</v>
       </c>
       <c r="F44">
-        <v>65.52</v>
+        <v>67.08</v>
       </c>
       <c r="G44">
         <v>21.2</v>
@@ -5017,28 +5017,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M44">
-        <v>4.966416</v>
+        <v>5.084664</v>
       </c>
       <c r="N44">
-        <v>5.59469511111111</v>
+        <v>5.47644711111111</v>
       </c>
       <c r="O44">
-        <v>0.5594695111111111</v>
+        <v>0.547644711111111</v>
       </c>
       <c r="P44">
-        <v>5.0352256</v>
+        <v>4.928802399999999</v>
       </c>
       <c r="Q44">
-        <v>6.585225599999999</v>
+        <v>6.478802399999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1116680444107772</v>
+        <v>0.1127536621079112</v>
       </c>
       <c r="T44">
-        <v>1.320236685534872</v>
+        <v>1.341996437521492</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.126505534597003</v>
+        <v>2.077051917513352</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0936041874015094</v>
+        <v>0.09378850904476801</v>
       </c>
       <c r="C45">
-        <v>76.69084732929771</v>
+        <v>74.85669814575697</v>
       </c>
       <c r="D45">
-        <v>122.5708473292977</v>
+        <v>122.296698145757</v>
       </c>
       <c r="E45">
-        <v>50.48</v>
+        <v>52.04</v>
       </c>
       <c r="F45">
-        <v>67.08</v>
+        <v>68.64</v>
       </c>
       <c r="G45">
         <v>21.2</v>
@@ -5099,28 +5099,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M45">
-        <v>5.084664</v>
+        <v>5.202912</v>
       </c>
       <c r="N45">
-        <v>5.47644711111111</v>
+        <v>5.35819911111111</v>
       </c>
       <c r="O45">
-        <v>0.547644711111111</v>
+        <v>0.5358199111111109</v>
       </c>
       <c r="P45">
-        <v>4.928802399999999</v>
+        <v>4.822379199999999</v>
       </c>
       <c r="Q45">
-        <v>6.478802399999998</v>
+        <v>6.372379199999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1127536621079112</v>
+        <v>0.1138780518656572</v>
       </c>
       <c r="T45">
-        <v>1.341996437521492</v>
+        <v>1.364533323507634</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.077051917513352</v>
+        <v>2.029846192115321</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09378850904476801</v>
+        <v>0.09972383068802662</v>
       </c>
       <c r="C46">
-        <v>74.85669814575697</v>
+        <v>65.08035519356154</v>
       </c>
       <c r="D46">
-        <v>122.296698145757</v>
+        <v>114.0803551935615</v>
       </c>
       <c r="E46">
-        <v>52.04</v>
+        <v>53.6</v>
       </c>
       <c r="F46">
-        <v>68.64</v>
+        <v>70.2</v>
       </c>
       <c r="G46">
         <v>21.2</v>
@@ -5181,45 +5181,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M46">
-        <v>5.202912</v>
+        <v>6.318</v>
       </c>
       <c r="N46">
-        <v>5.35819911111111</v>
+        <v>4.24311111111111</v>
       </c>
       <c r="O46">
-        <v>0.5358199111111109</v>
+        <v>0.4243111111111111</v>
       </c>
       <c r="P46">
-        <v>4.822379199999999</v>
+        <v>3.8188</v>
       </c>
       <c r="Q46">
-        <v>6.372379199999998</v>
+        <v>5.368799999999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1138780518656572</v>
+        <v>0.1150433285236848</v>
       </c>
       <c r="T46">
-        <v>1.364533323507634</v>
+        <v>1.387889732620545</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.1</v>
       </c>
       <c r="W46">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.029846192115321</v>
+        <v>1.671590869121733</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09972383068802662</v>
+        <v>0.1000359523312852</v>
       </c>
       <c r="C47">
-        <v>65.08035519356154</v>
+        <v>63.11872841708195</v>
       </c>
       <c r="D47">
-        <v>114.0803551935615</v>
+        <v>113.678728417082</v>
       </c>
       <c r="E47">
-        <v>53.6</v>
+        <v>55.16</v>
       </c>
       <c r="F47">
-        <v>70.2</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="G47">
         <v>21.2</v>
@@ -5263,28 +5263,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M47">
-        <v>6.318</v>
+        <v>6.4584</v>
       </c>
       <c r="N47">
-        <v>4.24311111111111</v>
+        <v>4.10271111111111</v>
       </c>
       <c r="O47">
-        <v>0.4243111111111111</v>
+        <v>0.410271111111111</v>
       </c>
       <c r="P47">
-        <v>3.8188</v>
+        <v>3.692439999999999</v>
       </c>
       <c r="Q47">
-        <v>5.368799999999999</v>
+        <v>5.242439999999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1150433285236848</v>
+        <v>0.1162517635764541</v>
       </c>
       <c r="T47">
-        <v>1.387889732620545</v>
+        <v>1.412111193922824</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.671590869121733</v>
+        <v>1.635251937184304</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1000359523312852</v>
+        <v>0.1003480739745439</v>
       </c>
       <c r="C48">
-        <v>63.11872841708195</v>
+        <v>61.15991962234604</v>
       </c>
       <c r="D48">
-        <v>113.678728417082</v>
+        <v>113.2799196223461</v>
       </c>
       <c r="E48">
-        <v>55.16</v>
+        <v>56.72000000000001</v>
       </c>
       <c r="F48">
-        <v>71.76000000000001</v>
+        <v>73.32000000000001</v>
       </c>
       <c r="G48">
         <v>21.2</v>
@@ -5345,28 +5345,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M48">
-        <v>6.4584</v>
+        <v>6.598800000000001</v>
       </c>
       <c r="N48">
-        <v>4.10271111111111</v>
+        <v>3.962311111111109</v>
       </c>
       <c r="O48">
-        <v>0.410271111111111</v>
+        <v>0.396231111111111</v>
       </c>
       <c r="P48">
-        <v>3.692439999999999</v>
+        <v>3.566079999999999</v>
       </c>
       <c r="Q48">
-        <v>5.242439999999998</v>
+        <v>5.116079999999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1162517635764541</v>
+        <v>0.1175057999519695</v>
       </c>
       <c r="T48">
-        <v>1.412111193922824</v>
+        <v>1.437246672632736</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.635251937184304</v>
+        <v>1.600459342776127</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1003480739745439</v>
+        <v>0.1006601956178025</v>
       </c>
       <c r="C49">
-        <v>61.15991962234604</v>
+        <v>59.20389925482634</v>
       </c>
       <c r="D49">
-        <v>113.2799196223461</v>
+        <v>112.8838992548263</v>
       </c>
       <c r="E49">
-        <v>56.72000000000001</v>
+        <v>58.28000000000001</v>
       </c>
       <c r="F49">
-        <v>73.32000000000001</v>
+        <v>74.88000000000001</v>
       </c>
       <c r="G49">
         <v>21.2</v>
@@ -5427,28 +5427,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M49">
-        <v>6.598800000000001</v>
+        <v>6.7392</v>
       </c>
       <c r="N49">
-        <v>3.962311111111109</v>
+        <v>3.82191111111111</v>
       </c>
       <c r="O49">
-        <v>0.396231111111111</v>
+        <v>0.382191111111111</v>
       </c>
       <c r="P49">
-        <v>3.566079999999999</v>
+        <v>3.439719999999999</v>
       </c>
       <c r="Q49">
-        <v>5.116079999999998</v>
+        <v>4.989719999999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1175057999519695</v>
+        <v>0.118808068495774</v>
       </c>
       <c r="T49">
-        <v>1.437246672632736</v>
+        <v>1.463348900523797</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.600459342776127</v>
+        <v>1.567116439801625</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1006601956178025</v>
+        <v>0.1009723172610611</v>
       </c>
       <c r="C50">
-        <v>59.20389925482635</v>
+        <v>57.2506381718396</v>
       </c>
       <c r="D50">
-        <v>112.8838992548264</v>
+        <v>112.4906381718396</v>
       </c>
       <c r="E50">
-        <v>58.27999999999999</v>
+        <v>59.84</v>
       </c>
       <c r="F50">
-        <v>74.88</v>
+        <v>76.44</v>
       </c>
       <c r="G50">
         <v>21.2</v>
@@ -5509,28 +5509,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M50">
-        <v>6.739199999999999</v>
+        <v>6.8796</v>
       </c>
       <c r="N50">
-        <v>3.821911111111111</v>
+        <v>3.68151111111111</v>
       </c>
       <c r="O50">
-        <v>0.3821911111111111</v>
+        <v>0.368151111111111</v>
       </c>
       <c r="P50">
-        <v>3.439719999999999</v>
+        <v>3.313359999999999</v>
       </c>
       <c r="Q50">
-        <v>4.989719999999999</v>
+        <v>4.863359999999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1188080684957739</v>
+        <v>0.1201614063942374</v>
       </c>
       <c r="T50">
-        <v>1.463348900523797</v>
+        <v>1.490474745194901</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.567116439801625</v>
+        <v>1.535134471642408</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1009723172610611</v>
+        <v>0.1012844389043197</v>
       </c>
       <c r="C51">
-        <v>57.2506381718396</v>
+        <v>55.30010763539778</v>
       </c>
       <c r="D51">
-        <v>112.4906381718396</v>
+        <v>112.1001076353978</v>
       </c>
       <c r="E51">
-        <v>59.84</v>
+        <v>61.4</v>
       </c>
       <c r="F51">
-        <v>76.44</v>
+        <v>78</v>
       </c>
       <c r="G51">
         <v>21.2</v>
@@ -5591,28 +5591,28 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M51">
-        <v>6.8796</v>
+        <v>7.02</v>
       </c>
       <c r="N51">
-        <v>3.68151111111111</v>
+        <v>3.54111111111111</v>
       </c>
       <c r="O51">
-        <v>0.368151111111111</v>
+        <v>0.354111111111111</v>
       </c>
       <c r="P51">
-        <v>3.313359999999999</v>
+        <v>3.186999999999999</v>
       </c>
       <c r="Q51">
-        <v>4.863359999999999</v>
+        <v>4.736999999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1201614063942374</v>
+        <v>0.1215688778086393</v>
       </c>
       <c r="T51">
-        <v>1.490474745194901</v>
+        <v>1.518685623652848</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.535134471642408</v>
+        <v>1.50443178220956</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1012844389043197</v>
+        <v>0.1285793523940063</v>
       </c>
       <c r="C52">
-        <v>55.30010763539778</v>
+        <v>27.63296332144773</v>
       </c>
       <c r="D52">
-        <v>112.1001076353978</v>
+        <v>85.99296332144773</v>
       </c>
       <c r="E52">
-        <v>61.4</v>
+        <v>62.96</v>
       </c>
       <c r="F52">
-        <v>78</v>
+        <v>79.56</v>
       </c>
       <c r="G52">
         <v>21.2</v>
@@ -5673,45 +5673,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M52">
-        <v>7.02</v>
+        <v>11.679408</v>
       </c>
       <c r="N52">
-        <v>3.54111111111111</v>
+        <v>-1.118296888888892</v>
       </c>
       <c r="O52">
-        <v>0.354111111111111</v>
+        <v>-0.1118296888888892</v>
       </c>
       <c r="P52">
-        <v>3.186999999999999</v>
+        <v>-1.006467200000003</v>
       </c>
       <c r="Q52">
-        <v>4.736999999999999</v>
+        <v>0.543532799999997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1215688778086393</v>
+        <v>0.1234312151305088</v>
       </c>
       <c r="T52">
-        <v>1.518685623652848</v>
+        <v>1.55601367969531</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1</v>
+        <v>0.09042505502942537</v>
       </c>
       <c r="W52">
-        <v>0.081</v>
+        <v>0.1335256019216804</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.50443178220956</v>
+        <v>0.9042505502942536</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1285793523940063</v>
+        <v>0.1295893523940063</v>
       </c>
       <c r="C53">
-        <v>27.63296332144773</v>
+        <v>25.33823072490857</v>
       </c>
       <c r="D53">
-        <v>85.99296332144773</v>
+        <v>85.25823072490857</v>
       </c>
       <c r="E53">
-        <v>62.96</v>
+        <v>64.52000000000001</v>
       </c>
       <c r="F53">
-        <v>79.56</v>
+        <v>81.12</v>
       </c>
       <c r="G53">
         <v>21.2</v>
@@ -5755,37 +5755,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M53">
-        <v>11.679408</v>
+        <v>11.908416</v>
       </c>
       <c r="N53">
-        <v>-1.118296888888892</v>
+        <v>-1.347304888888893</v>
       </c>
       <c r="O53">
-        <v>-0.1118296888888892</v>
+        <v>-0.1347304888888892</v>
       </c>
       <c r="P53">
-        <v>-1.006467200000003</v>
+        <v>-1.212574400000003</v>
       </c>
       <c r="Q53">
-        <v>0.543532799999997</v>
+        <v>0.3374255999999967</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1234312151305088</v>
+        <v>0.1250485321123944</v>
       </c>
       <c r="T53">
-        <v>1.55601367969531</v>
+        <v>1.588430631355629</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.09042505502942537</v>
+        <v>0.08868611166347488</v>
       </c>
       <c r="W53">
-        <v>0.1335256019216804</v>
+        <v>0.1337808788078019</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9042505502942536</v>
+        <v>0.8868611166347488</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1295893523940063</v>
+        <v>0.1305993523940063</v>
       </c>
       <c r="C54">
-        <v>25.33823072490857</v>
+        <v>23.05594702333205</v>
       </c>
       <c r="D54">
-        <v>85.25823072490857</v>
+        <v>84.53594702333206</v>
       </c>
       <c r="E54">
-        <v>64.52000000000001</v>
+        <v>66.08000000000001</v>
       </c>
       <c r="F54">
-        <v>81.12</v>
+        <v>82.68000000000001</v>
       </c>
       <c r="G54">
         <v>21.2</v>
@@ -5837,37 +5837,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M54">
-        <v>11.908416</v>
+        <v>12.137424</v>
       </c>
       <c r="N54">
-        <v>-1.347304888888893</v>
+        <v>-1.576312888888893</v>
       </c>
       <c r="O54">
-        <v>-0.1347304888888892</v>
+        <v>-0.1576312888888893</v>
       </c>
       <c r="P54">
-        <v>-1.212574400000003</v>
+        <v>-1.418681600000004</v>
       </c>
       <c r="Q54">
-        <v>0.3374255999999967</v>
+        <v>0.1313183999999965</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1250485321123944</v>
+        <v>0.1267346710935092</v>
       </c>
       <c r="T54">
-        <v>1.588430631355629</v>
+        <v>1.622227027767451</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.08868611166347488</v>
+        <v>0.08701278880189989</v>
       </c>
       <c r="W54">
-        <v>0.1337808788078019</v>
+        <v>0.1340265226038811</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8868611166347488</v>
+        <v>0.8701278880189987</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1305993523940063</v>
+        <v>0.1316093523940063</v>
       </c>
       <c r="C55">
-        <v>23.05594702333205</v>
+        <v>20.78579848398485</v>
       </c>
       <c r="D55">
-        <v>84.53594702333206</v>
+        <v>83.82579848398485</v>
       </c>
       <c r="E55">
-        <v>66.08000000000001</v>
+        <v>67.64000000000001</v>
       </c>
       <c r="F55">
-        <v>82.68000000000001</v>
+        <v>84.24000000000001</v>
       </c>
       <c r="G55">
         <v>21.2</v>
@@ -5919,37 +5919,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M55">
-        <v>12.137424</v>
+        <v>12.366432</v>
       </c>
       <c r="N55">
-        <v>-1.576312888888893</v>
+        <v>-1.805320888888893</v>
       </c>
       <c r="O55">
-        <v>-0.1576312888888893</v>
+        <v>-0.1805320888888893</v>
       </c>
       <c r="P55">
-        <v>-1.418681600000004</v>
+        <v>-1.624788800000004</v>
       </c>
       <c r="Q55">
-        <v>0.1313183999999965</v>
+        <v>-0.07478880000000387</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1267346710935092</v>
+        <v>0.1284941204651072</v>
       </c>
       <c r="T55">
-        <v>1.622227027767451</v>
+        <v>1.657492832718917</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.08701278880189989</v>
+        <v>0.08540144086112395</v>
       </c>
       <c r="W55">
-        <v>0.1340265226038811</v>
+        <v>0.134263068481587</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8701278880189987</v>
+        <v>0.8540144086112395</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1316093523940063</v>
+        <v>0.1326193523940063</v>
       </c>
       <c r="C56">
-        <v>20.78579848398485</v>
+        <v>18.52748182842322</v>
       </c>
       <c r="D56">
-        <v>83.82579848398485</v>
+        <v>83.12748182842323</v>
       </c>
       <c r="E56">
-        <v>67.64000000000001</v>
+        <v>69.20000000000002</v>
       </c>
       <c r="F56">
-        <v>84.24000000000001</v>
+        <v>85.80000000000001</v>
       </c>
       <c r="G56">
         <v>21.2</v>
@@ -6001,37 +6001,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M56">
-        <v>12.366432</v>
+        <v>12.59544</v>
       </c>
       <c r="N56">
-        <v>-1.805320888888893</v>
+        <v>-2.034328888888894</v>
       </c>
       <c r="O56">
-        <v>-0.1805320888888893</v>
+        <v>-0.2034328888888894</v>
       </c>
       <c r="P56">
-        <v>-1.624788800000004</v>
+        <v>-1.830896000000004</v>
       </c>
       <c r="Q56">
-        <v>-0.07478880000000387</v>
+        <v>-0.280896000000004</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1284941204651072</v>
+        <v>0.130331767586554</v>
       </c>
       <c r="T56">
-        <v>1.657492832718917</v>
+        <v>1.694326006779338</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.08540144086112395</v>
+        <v>0.0838486873909217</v>
       </c>
       <c r="W56">
-        <v>0.134263068481587</v>
+        <v>0.1344910126910127</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8540144086112395</v>
+        <v>0.8384868739092169</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1326193523940063</v>
+        <v>0.1336293523940063</v>
       </c>
       <c r="C57">
-        <v>18.52748182842322</v>
+        <v>16.28070380063977</v>
       </c>
       <c r="D57">
-        <v>83.12748182842323</v>
+        <v>82.44070380063978</v>
       </c>
       <c r="E57">
-        <v>69.20000000000002</v>
+        <v>70.76000000000002</v>
       </c>
       <c r="F57">
-        <v>85.80000000000001</v>
+        <v>87.36000000000001</v>
       </c>
       <c r="G57">
         <v>21.2</v>
@@ -6083,37 +6083,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M57">
-        <v>12.59544</v>
+        <v>12.824448</v>
       </c>
       <c r="N57">
-        <v>-2.034328888888894</v>
+        <v>-2.263336888888894</v>
       </c>
       <c r="O57">
-        <v>-0.2034328888888894</v>
+        <v>-0.2263336888888894</v>
       </c>
       <c r="P57">
-        <v>-1.830896000000004</v>
+        <v>-2.037003200000004</v>
       </c>
       <c r="Q57">
-        <v>-0.280896000000004</v>
+        <v>-0.4870032000000044</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.130331767586554</v>
+        <v>0.1322529441226121</v>
       </c>
       <c r="T57">
-        <v>1.694326006779338</v>
+        <v>1.732833416024322</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.0838486873909217</v>
+        <v>0.08235138940179809</v>
       </c>
       <c r="W57">
-        <v>0.1344910126910127</v>
+        <v>0.1347108160358161</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8384868739092169</v>
+        <v>0.8235138940179809</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1336293523940063</v>
+        <v>0.1346393523940063</v>
       </c>
       <c r="C58">
-        <v>16.28070380063977</v>
+        <v>14.04518075644152</v>
       </c>
       <c r="D58">
-        <v>82.44070380063978</v>
+        <v>81.76518075644154</v>
       </c>
       <c r="E58">
-        <v>70.76000000000002</v>
+        <v>72.32000000000002</v>
       </c>
       <c r="F58">
-        <v>87.36000000000001</v>
+        <v>88.92000000000002</v>
       </c>
       <c r="G58">
         <v>21.2</v>
@@ -6165,37 +6165,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M58">
-        <v>12.824448</v>
+        <v>13.053456</v>
       </c>
       <c r="N58">
-        <v>-2.263336888888894</v>
+        <v>-2.492344888888894</v>
       </c>
       <c r="O58">
-        <v>-0.2263336888888894</v>
+        <v>-0.2492344888888894</v>
       </c>
       <c r="P58">
-        <v>-2.037003200000004</v>
+        <v>-2.243110400000005</v>
       </c>
       <c r="Q58">
-        <v>-0.4870032000000044</v>
+        <v>-0.6931104000000048</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1322529441226121</v>
+        <v>0.1342634777068589</v>
       </c>
       <c r="T58">
-        <v>1.732833416024322</v>
+        <v>1.773131867559772</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.08235138940179809</v>
+        <v>0.08090662818422269</v>
       </c>
       <c r="W58">
-        <v>0.1347108160358161</v>
+        <v>0.1349229069825561</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8235138940179809</v>
+        <v>0.8090662818422268</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1346393523940063</v>
+        <v>0.167463920679274</v>
       </c>
       <c r="C59">
-        <v>14.04518075644152</v>
+        <v>-4.710005253800162</v>
       </c>
       <c r="D59">
-        <v>81.76518075644154</v>
+        <v>64.56999474619985</v>
       </c>
       <c r="E59">
-        <v>72.32000000000002</v>
+        <v>73.88000000000002</v>
       </c>
       <c r="F59">
-        <v>88.92000000000002</v>
+        <v>90.48000000000002</v>
       </c>
       <c r="G59">
         <v>21.2</v>
@@ -6247,45 +6247,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M59">
-        <v>13.053456</v>
+        <v>18.168384</v>
       </c>
       <c r="N59">
-        <v>-2.492344888888894</v>
+        <v>-7.607272888888893</v>
       </c>
       <c r="O59">
-        <v>-0.2492344888888894</v>
+        <v>-0.7607272888888894</v>
       </c>
       <c r="P59">
-        <v>-2.243110400000005</v>
+        <v>-6.846545600000004</v>
       </c>
       <c r="Q59">
-        <v>-0.6931104000000048</v>
+        <v>-5.296545600000004</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1342634777068589</v>
+        <v>0.1375472945219452</v>
       </c>
       <c r="T59">
-        <v>1.773131867559772</v>
+        <v>1.838951575228881</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08090662818422269</v>
+        <v>0.05812906151208114</v>
       </c>
       <c r="W59">
-        <v>0.1349229069825561</v>
+        <v>0.1891276844483741</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8090662818422268</v>
+        <v>0.5812906151208115</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.167463920679274</v>
+        <v>0.169013920679274</v>
       </c>
       <c r="C60">
-        <v>-4.710005253800134</v>
+        <v>-6.904912691785896</v>
       </c>
       <c r="D60">
-        <v>64.56999474619985</v>
+        <v>63.9350873082141</v>
       </c>
       <c r="E60">
-        <v>73.88</v>
+        <v>75.44</v>
       </c>
       <c r="F60">
-        <v>90.47999999999999</v>
+        <v>92.03999999999999</v>
       </c>
       <c r="G60">
         <v>21.2</v>
@@ -6329,37 +6329,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M60">
-        <v>18.168384</v>
+        <v>18.481632</v>
       </c>
       <c r="N60">
-        <v>-7.60727288888889</v>
+        <v>-7.920520888888888</v>
       </c>
       <c r="O60">
-        <v>-0.760727288888889</v>
+        <v>-0.7920520888888888</v>
       </c>
       <c r="P60">
-        <v>-6.846545600000001</v>
+        <v>-7.128468799999998</v>
       </c>
       <c r="Q60">
-        <v>-5.296545600000001</v>
+        <v>-5.578468799999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1375472945219452</v>
+        <v>0.1397850334127244</v>
       </c>
       <c r="T60">
-        <v>1.838951575228881</v>
+        <v>1.883804052673488</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05812906151208115</v>
+        <v>0.05714382318136792</v>
       </c>
       <c r="W60">
-        <v>0.1891276844483741</v>
+        <v>0.1893255203051813</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5812906151208115</v>
+        <v>0.5714382318136793</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.169013920679274</v>
+        <v>0.170563920679274</v>
       </c>
       <c r="C61">
-        <v>-6.904912691785896</v>
+        <v>-9.087455800056972</v>
       </c>
       <c r="D61">
-        <v>63.9350873082141</v>
+        <v>63.31254419994303</v>
       </c>
       <c r="E61">
-        <v>75.44</v>
+        <v>77</v>
       </c>
       <c r="F61">
-        <v>92.03999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="G61">
         <v>21.2</v>
@@ -6411,37 +6411,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M61">
-        <v>18.481632</v>
+        <v>18.79488</v>
       </c>
       <c r="N61">
-        <v>-7.920520888888888</v>
+        <v>-8.233768888888889</v>
       </c>
       <c r="O61">
-        <v>-0.7920520888888888</v>
+        <v>-0.8233768888888889</v>
       </c>
       <c r="P61">
-        <v>-7.128468799999998</v>
+        <v>-7.410392</v>
       </c>
       <c r="Q61">
-        <v>-5.578468799999999</v>
+        <v>-5.860392</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1397850334127244</v>
+        <v>0.1421346592480425</v>
       </c>
       <c r="T61">
-        <v>1.883804052673488</v>
+        <v>1.930899153990325</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05714382318136792</v>
+        <v>0.05619142612834511</v>
       </c>
       <c r="W61">
-        <v>0.1893255203051813</v>
+        <v>0.1895167616334283</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5714382318136793</v>
+        <v>0.5619142612834511</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.170563920679274</v>
+        <v>0.172113920679274</v>
       </c>
       <c r="C62">
-        <v>-9.087455800056972</v>
+        <v>-11.25799227428166</v>
       </c>
       <c r="D62">
-        <v>63.31254419994303</v>
+        <v>62.70200772571834</v>
       </c>
       <c r="E62">
-        <v>77</v>
+        <v>78.56</v>
       </c>
       <c r="F62">
-        <v>93.59999999999999</v>
+        <v>95.16</v>
       </c>
       <c r="G62">
         <v>21.2</v>
@@ -6493,37 +6493,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M62">
-        <v>18.79488</v>
+        <v>19.108128</v>
       </c>
       <c r="N62">
-        <v>-8.233768888888889</v>
+        <v>-8.547016888888891</v>
       </c>
       <c r="O62">
-        <v>-0.8233768888888889</v>
+        <v>-0.8547016888888891</v>
       </c>
       <c r="P62">
-        <v>-7.410392</v>
+        <v>-7.692315200000001</v>
       </c>
       <c r="Q62">
-        <v>-5.860392</v>
+        <v>-6.142315200000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1421346592480425</v>
+        <v>0.144604778715941</v>
       </c>
       <c r="T62">
-        <v>1.930899153990325</v>
+        <v>1.980409388708026</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05619142612834511</v>
+        <v>0.05527025520820831</v>
       </c>
       <c r="W62">
-        <v>0.1895167616334283</v>
+        <v>0.1897017327541918</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5619142612834511</v>
+        <v>0.5527025520820831</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.172113920679274</v>
+        <v>0.173663920679274</v>
       </c>
       <c r="C63">
-        <v>-11.25799227428166</v>
+        <v>-13.41686614456337</v>
       </c>
       <c r="D63">
-        <v>62.70200772571834</v>
+        <v>62.10313385543662</v>
       </c>
       <c r="E63">
-        <v>78.56</v>
+        <v>80.12</v>
       </c>
       <c r="F63">
-        <v>95.16</v>
+        <v>96.72</v>
       </c>
       <c r="G63">
         <v>21.2</v>
@@ -6575,37 +6575,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M63">
-        <v>19.108128</v>
+        <v>19.421376</v>
       </c>
       <c r="N63">
-        <v>-8.547016888888891</v>
+        <v>-8.860264888888889</v>
       </c>
       <c r="O63">
-        <v>-0.8547016888888891</v>
+        <v>-0.8860264888888889</v>
       </c>
       <c r="P63">
-        <v>-7.692315200000001</v>
+        <v>-7.9742384</v>
       </c>
       <c r="Q63">
-        <v>-6.142315200000001</v>
+        <v>-6.4242384</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.144604778715941</v>
+        <v>0.1472049044716237</v>
       </c>
       <c r="T63">
-        <v>1.980409388708026</v>
+        <v>2.032525425252974</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05527025520820831</v>
+        <v>0.05437879947904366</v>
       </c>
       <c r="W63">
-        <v>0.1897017327541918</v>
+        <v>0.189880737064608</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5527025520820831</v>
+        <v>0.5437879947904366</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.173663920679274</v>
+        <v>0.175213920679274</v>
       </c>
       <c r="C64">
-        <v>-13.41686614456337</v>
+        <v>-15.56440842187313</v>
       </c>
       <c r="D64">
-        <v>62.10313385543662</v>
+        <v>61.51559157812687</v>
       </c>
       <c r="E64">
-        <v>80.12</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F64">
-        <v>96.72</v>
+        <v>98.28</v>
       </c>
       <c r="G64">
         <v>21.2</v>
@@ -6657,37 +6657,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M64">
-        <v>19.421376</v>
+        <v>19.734624</v>
       </c>
       <c r="N64">
-        <v>-8.860264888888889</v>
+        <v>-9.17351288888889</v>
       </c>
       <c r="O64">
-        <v>-0.8860264888888889</v>
+        <v>-0.9173512888888891</v>
       </c>
       <c r="P64">
-        <v>-7.9742384</v>
+        <v>-8.2561616</v>
       </c>
       <c r="Q64">
-        <v>-6.4242384</v>
+        <v>-6.706161600000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1472049044716237</v>
+        <v>0.1499455775654513</v>
       </c>
       <c r="T64">
-        <v>2.032525425252974</v>
+        <v>2.087458544854405</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05437879947904366</v>
+        <v>0.05351564393175726</v>
       </c>
       <c r="W64">
-        <v>0.189880737064608</v>
+        <v>0.1900540586985031</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5437879947904366</v>
+        <v>0.5351564393175725</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.175213920679274</v>
+        <v>0.176763920679274</v>
       </c>
       <c r="C65">
-        <v>-15.56440842187313</v>
+        <v>-17.70093770813156</v>
       </c>
       <c r="D65">
-        <v>61.51559157812687</v>
+        <v>60.93906229186845</v>
       </c>
       <c r="E65">
-        <v>81.68000000000001</v>
+        <v>83.24000000000001</v>
       </c>
       <c r="F65">
-        <v>98.28</v>
+        <v>99.84</v>
       </c>
       <c r="G65">
         <v>21.2</v>
@@ -6739,37 +6739,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M65">
-        <v>19.734624</v>
+        <v>20.047872</v>
       </c>
       <c r="N65">
-        <v>-9.17351288888889</v>
+        <v>-9.486760888888892</v>
       </c>
       <c r="O65">
-        <v>-0.9173512888888891</v>
+        <v>-0.9486760888888892</v>
       </c>
       <c r="P65">
-        <v>-8.2561616</v>
+        <v>-8.538084800000002</v>
       </c>
       <c r="Q65">
-        <v>-6.706161600000001</v>
+        <v>-6.988084800000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1499455775654513</v>
+        <v>0.1528385102756028</v>
       </c>
       <c r="T65">
-        <v>2.087458544854405</v>
+        <v>2.145443504433695</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05351564393175726</v>
+        <v>0.05267946199532354</v>
       </c>
       <c r="W65">
-        <v>0.1900540586985031</v>
+        <v>0.190221964031339</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5351564393175725</v>
+        <v>0.5267946199532354</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.176763920679274</v>
+        <v>0.178313920679274</v>
       </c>
       <c r="C66">
-        <v>-17.70093770813156</v>
+        <v>-19.82676077230298</v>
       </c>
       <c r="D66">
-        <v>60.93906229186845</v>
+        <v>60.37323922769703</v>
       </c>
       <c r="E66">
-        <v>83.24000000000001</v>
+        <v>84.80000000000001</v>
       </c>
       <c r="F66">
-        <v>99.84</v>
+        <v>101.4</v>
       </c>
       <c r="G66">
         <v>21.2</v>
@@ -6821,37 +6821,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M66">
-        <v>20.047872</v>
+        <v>20.36112</v>
       </c>
       <c r="N66">
-        <v>-9.486760888888892</v>
+        <v>-9.800008888888893</v>
       </c>
       <c r="O66">
-        <v>-0.9486760888888892</v>
+        <v>-0.9800008888888894</v>
       </c>
       <c r="P66">
-        <v>-8.538084800000002</v>
+        <v>-8.820008000000003</v>
       </c>
       <c r="Q66">
-        <v>-6.988084800000002</v>
+        <v>-7.270008000000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1528385102756028</v>
+        <v>0.1558967534263343</v>
       </c>
       <c r="T66">
-        <v>2.145443504433695</v>
+        <v>2.206741890274658</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.05267946199532354</v>
+        <v>0.05186900873385702</v>
       </c>
       <c r="W66">
-        <v>0.190221964031339</v>
+        <v>0.1903847030462415</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5267946199532354</v>
+        <v>0.5186900873385702</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.178313920679274</v>
+        <v>0.179863920679274</v>
       </c>
       <c r="C67">
-        <v>-19.82676077230298</v>
+        <v>-21.94217309469038</v>
       </c>
       <c r="D67">
-        <v>60.37323922769703</v>
+        <v>59.81782690530964</v>
       </c>
       <c r="E67">
-        <v>84.80000000000001</v>
+        <v>86.36000000000001</v>
       </c>
       <c r="F67">
-        <v>101.4</v>
+        <v>102.96</v>
       </c>
       <c r="G67">
         <v>21.2</v>
@@ -6903,37 +6903,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M67">
-        <v>20.36112</v>
+        <v>20.674368</v>
       </c>
       <c r="N67">
-        <v>-9.800008888888893</v>
+        <v>-10.11325688888889</v>
       </c>
       <c r="O67">
-        <v>-0.9800008888888894</v>
+        <v>-1.011325688888889</v>
       </c>
       <c r="P67">
-        <v>-8.820008000000003</v>
+        <v>-9.101931200000003</v>
       </c>
       <c r="Q67">
-        <v>-7.270008000000003</v>
+        <v>-7.551931200000003</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1558967534263343</v>
+        <v>0.1591348932329912</v>
       </c>
       <c r="T67">
-        <v>2.206741890274658</v>
+        <v>2.27164606351803</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.05186900873385702</v>
+        <v>0.05108311466213192</v>
       </c>
       <c r="W67">
-        <v>0.1903847030462415</v>
+        <v>0.1905425105758439</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5186900873385702</v>
+        <v>0.5108311466213191</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.179863920679274</v>
+        <v>0.181413920679274</v>
       </c>
       <c r="C68">
-        <v>-21.94217309469038</v>
+        <v>-24.04745938146033</v>
       </c>
       <c r="D68">
-        <v>59.81782690530964</v>
+        <v>59.27254061853969</v>
       </c>
       <c r="E68">
-        <v>86.36000000000001</v>
+        <v>87.92000000000002</v>
       </c>
       <c r="F68">
-        <v>102.96</v>
+        <v>104.52</v>
       </c>
       <c r="G68">
         <v>21.2</v>
@@ -6985,37 +6985,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M68">
-        <v>20.674368</v>
+        <v>20.987616</v>
       </c>
       <c r="N68">
-        <v>-10.11325688888889</v>
+        <v>-10.42650488888889</v>
       </c>
       <c r="O68">
-        <v>-1.011325688888889</v>
+        <v>-1.042650488888889</v>
       </c>
       <c r="P68">
-        <v>-9.101931200000003</v>
+        <v>-9.383854400000004</v>
       </c>
       <c r="Q68">
-        <v>-7.551931200000003</v>
+        <v>-7.833854400000004</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1591348932329912</v>
+        <v>0.1625692839370212</v>
       </c>
       <c r="T68">
-        <v>2.27164606351803</v>
+        <v>2.340483823018576</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.05108311466213192</v>
+        <v>0.05032068011493591</v>
       </c>
       <c r="W68">
-        <v>0.1905425105758439</v>
+        <v>0.1906956074329209</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5108311466213191</v>
+        <v>0.5032068011493591</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.181413920679274</v>
+        <v>0.2069634849561019</v>
       </c>
       <c r="C69">
-        <v>-24.04745938146033</v>
+        <v>-33.35034709504488</v>
       </c>
       <c r="D69">
-        <v>59.27254061853969</v>
+        <v>51.52965290495514</v>
       </c>
       <c r="E69">
-        <v>87.92000000000002</v>
+        <v>89.48000000000002</v>
       </c>
       <c r="F69">
-        <v>104.52</v>
+        <v>106.08</v>
       </c>
       <c r="G69">
         <v>21.2</v>
@@ -7067,45 +7067,45 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M69">
-        <v>20.987616</v>
+        <v>25.01366400000001</v>
       </c>
       <c r="N69">
-        <v>-10.42650488888889</v>
+        <v>-14.4525528888889</v>
       </c>
       <c r="O69">
-        <v>-1.042650488888889</v>
+        <v>-1.44525528888889</v>
       </c>
       <c r="P69">
-        <v>-9.383854400000004</v>
+        <v>-13.00729760000001</v>
       </c>
       <c r="Q69">
-        <v>-7.833854400000004</v>
+        <v>-11.45729760000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1625692839370212</v>
+        <v>0.1668419624251404</v>
       </c>
       <c r="T69">
-        <v>2.340483823018576</v>
+        <v>2.426123937826473</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05032068011493591</v>
+        <v>0.04222136793358666</v>
       </c>
       <c r="W69">
-        <v>0.1906956074329209</v>
+        <v>0.2258442014412603</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5032068011493591</v>
+        <v>0.4222136793358665</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2069634849561019</v>
+        <v>0.2088634849561019</v>
       </c>
       <c r="C70">
-        <v>-33.35034709504488</v>
+        <v>-35.40611471040458</v>
       </c>
       <c r="D70">
-        <v>51.52965290495514</v>
+        <v>51.03388528959543</v>
       </c>
       <c r="E70">
-        <v>89.48000000000002</v>
+        <v>91.04000000000002</v>
       </c>
       <c r="F70">
-        <v>106.08</v>
+        <v>107.64</v>
       </c>
       <c r="G70">
         <v>21.2</v>
@@ -7149,37 +7149,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M70">
-        <v>25.01366400000001</v>
+        <v>25.381512</v>
       </c>
       <c r="N70">
-        <v>-14.4525528888889</v>
+        <v>-14.82040088888889</v>
       </c>
       <c r="O70">
-        <v>-1.44525528888889</v>
+        <v>-1.48204008888889</v>
       </c>
       <c r="P70">
-        <v>-13.00729760000001</v>
+        <v>-13.3383608</v>
       </c>
       <c r="Q70">
-        <v>-11.45729760000001</v>
+        <v>-11.7883608</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1668419624251404</v>
+        <v>0.1707465418582094</v>
       </c>
       <c r="T70">
-        <v>2.426123937826473</v>
+        <v>2.504386000337005</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04222136793358666</v>
+        <v>0.04160946405049119</v>
       </c>
       <c r="W70">
-        <v>0.2258442014412603</v>
+        <v>0.2259884883768942</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4222136793358665</v>
+        <v>0.416094640504912</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2088634849561019</v>
+        <v>0.2107634849561019</v>
       </c>
       <c r="C71">
-        <v>-35.40611471040458</v>
+        <v>-37.45243365524971</v>
       </c>
       <c r="D71">
-        <v>51.03388528959543</v>
+        <v>50.54756634475031</v>
       </c>
       <c r="E71">
-        <v>91.04000000000002</v>
+        <v>92.60000000000002</v>
       </c>
       <c r="F71">
-        <v>107.64</v>
+        <v>109.2</v>
       </c>
       <c r="G71">
         <v>21.2</v>
@@ -7231,37 +7231,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M71">
-        <v>25.381512</v>
+        <v>25.74936000000001</v>
       </c>
       <c r="N71">
-        <v>-14.82040088888889</v>
+        <v>-15.1882488888889</v>
       </c>
       <c r="O71">
-        <v>-1.48204008888889</v>
+        <v>-1.51882488888889</v>
       </c>
       <c r="P71">
-        <v>-13.3383608</v>
+        <v>-13.66942400000001</v>
       </c>
       <c r="Q71">
-        <v>-11.7883608</v>
+        <v>-12.11942400000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1707465418582094</v>
+        <v>0.1749114265868164</v>
       </c>
       <c r="T71">
-        <v>2.504386000337005</v>
+        <v>2.587865533681571</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04160946405049119</v>
+        <v>0.04101504313548418</v>
       </c>
       <c r="W71">
-        <v>0.2259884883768942</v>
+        <v>0.2261286528286528</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.416094640504912</v>
+        <v>0.4101504313548417</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2107634849561019</v>
+        <v>0.2126634849561019</v>
       </c>
       <c r="C72">
-        <v>-37.45243365524971</v>
+        <v>-39.48957149844239</v>
       </c>
       <c r="D72">
-        <v>50.54756634475031</v>
+        <v>50.07042850155762</v>
       </c>
       <c r="E72">
-        <v>92.60000000000002</v>
+        <v>94.16</v>
       </c>
       <c r="F72">
-        <v>109.2</v>
+        <v>110.76</v>
       </c>
       <c r="G72">
         <v>21.2</v>
@@ -7313,37 +7313,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M72">
-        <v>25.74936000000001</v>
+        <v>26.117208</v>
       </c>
       <c r="N72">
-        <v>-15.1882488888889</v>
+        <v>-15.55609688888889</v>
       </c>
       <c r="O72">
-        <v>-1.51882488888889</v>
+        <v>-1.555609688888889</v>
       </c>
       <c r="P72">
-        <v>-13.66942400000001</v>
+        <v>-14.0004872</v>
       </c>
       <c r="Q72">
-        <v>-12.11942400000001</v>
+        <v>-12.4504872</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1749114265868164</v>
+        <v>0.1793635447449825</v>
       </c>
       <c r="T72">
-        <v>2.587865533681571</v>
+        <v>2.677102276222316</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04101504313548418</v>
+        <v>0.04043736647160412</v>
       </c>
       <c r="W72">
-        <v>0.2261286528286528</v>
+        <v>0.2262648689859958</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4101504313548417</v>
+        <v>0.4043736647160412</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2126634849561019</v>
+        <v>0.2145634849561019</v>
       </c>
       <c r="C73">
-        <v>-39.48957149844237</v>
+        <v>-41.51778580057665</v>
       </c>
       <c r="D73">
-        <v>50.07042850155762</v>
+        <v>49.60221419942334</v>
       </c>
       <c r="E73">
-        <v>94.16</v>
+        <v>95.72</v>
       </c>
       <c r="F73">
-        <v>110.76</v>
+        <v>112.32</v>
       </c>
       <c r="G73">
         <v>21.2</v>
@@ -7395,37 +7395,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M73">
-        <v>26.117208</v>
+        <v>26.485056</v>
       </c>
       <c r="N73">
-        <v>-15.55609688888889</v>
+        <v>-15.92394488888889</v>
       </c>
       <c r="O73">
-        <v>-1.555609688888889</v>
+        <v>-1.592394488888889</v>
       </c>
       <c r="P73">
-        <v>-14.0004872</v>
+        <v>-14.3315504</v>
       </c>
       <c r="Q73">
-        <v>-12.4504872</v>
+        <v>-12.7815504</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1793635447449825</v>
+        <v>0.1841336713430176</v>
       </c>
       <c r="T73">
-        <v>2.677102276222315</v>
+        <v>2.772713071801683</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04043736647160413</v>
+        <v>0.03987573638172073</v>
       </c>
       <c r="W73">
-        <v>0.2262648689859958</v>
+        <v>0.2263973013611903</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4043736647160413</v>
+        <v>0.3987573638172073</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2145634849561019</v>
+        <v>0.2164634849561019</v>
       </c>
       <c r="C74">
-        <v>-41.51778580057665</v>
+        <v>-43.53732457758557</v>
       </c>
       <c r="D74">
-        <v>49.60221419942334</v>
+        <v>49.14267542241443</v>
       </c>
       <c r="E74">
-        <v>95.72</v>
+        <v>97.28</v>
       </c>
       <c r="F74">
-        <v>112.32</v>
+        <v>113.88</v>
       </c>
       <c r="G74">
         <v>21.2</v>
@@ -7477,37 +7477,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M74">
-        <v>26.485056</v>
+        <v>26.852904</v>
       </c>
       <c r="N74">
-        <v>-15.92394488888889</v>
+        <v>-16.29179288888889</v>
       </c>
       <c r="O74">
-        <v>-1.592394488888889</v>
+        <v>-1.629179288888889</v>
       </c>
       <c r="P74">
-        <v>-14.3315504</v>
+        <v>-14.6626136</v>
       </c>
       <c r="Q74">
-        <v>-12.7815504</v>
+        <v>-13.1126136</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1841336713430176</v>
+        <v>0.1892571406520182</v>
       </c>
       <c r="T74">
-        <v>2.772713071801683</v>
+        <v>2.875406148535078</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03987573638172073</v>
+        <v>0.03932949341758758</v>
       </c>
       <c r="W74">
-        <v>0.2263973013611903</v>
+        <v>0.2265261054521328</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3987573638172073</v>
+        <v>0.3932949341758758</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2164634849561019</v>
+        <v>0.2183634849561019</v>
       </c>
       <c r="C75">
-        <v>-43.53732457758557</v>
+        <v>-45.5484267388142</v>
       </c>
       <c r="D75">
-        <v>49.14267542241443</v>
+        <v>48.69157326118579</v>
       </c>
       <c r="E75">
-        <v>97.28</v>
+        <v>98.84</v>
       </c>
       <c r="F75">
-        <v>113.88</v>
+        <v>115.44</v>
       </c>
       <c r="G75">
         <v>21.2</v>
@@ -7559,37 +7559,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M75">
-        <v>26.852904</v>
+        <v>27.220752</v>
       </c>
       <c r="N75">
-        <v>-16.29179288888889</v>
+        <v>-16.65964088888889</v>
       </c>
       <c r="O75">
-        <v>-1.629179288888889</v>
+        <v>-1.665964088888889</v>
       </c>
       <c r="P75">
-        <v>-14.6626136</v>
+        <v>-14.9936768</v>
       </c>
       <c r="Q75">
-        <v>-13.1126136</v>
+        <v>-13.4436768</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1892571406520182</v>
+        <v>0.1947747229847882</v>
       </c>
       <c r="T75">
-        <v>2.875406148535078</v>
+        <v>2.985998692709505</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03932949341758758</v>
+        <v>0.03879801377680936</v>
       </c>
       <c r="W75">
-        <v>0.2265261054521328</v>
+        <v>0.2266514283514284</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3932949341758758</v>
+        <v>0.3879801377680936</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2183634849561019</v>
+        <v>0.2202634849561019</v>
       </c>
       <c r="C76">
-        <v>-45.5484267388142</v>
+        <v>-47.55132250118476</v>
       </c>
       <c r="D76">
-        <v>48.69157326118579</v>
+        <v>48.24867749881524</v>
       </c>
       <c r="E76">
-        <v>98.84</v>
+        <v>100.4</v>
       </c>
       <c r="F76">
-        <v>115.44</v>
+        <v>117</v>
       </c>
       <c r="G76">
         <v>21.2</v>
@@ -7641,37 +7641,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M76">
-        <v>27.220752</v>
+        <v>27.5886</v>
       </c>
       <c r="N76">
-        <v>-16.65964088888889</v>
+        <v>-17.02748888888889</v>
       </c>
       <c r="O76">
-        <v>-1.665964088888889</v>
+        <v>-1.702748888888889</v>
       </c>
       <c r="P76">
-        <v>-14.9936768</v>
+        <v>-15.32474</v>
       </c>
       <c r="Q76">
-        <v>-13.4436768</v>
+        <v>-13.77474</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1947747229847882</v>
+        <v>0.2007337119041797</v>
       </c>
       <c r="T76">
-        <v>2.985998692709505</v>
+        <v>3.105438640417885</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03879801377680936</v>
+        <v>0.03828070692645191</v>
       </c>
       <c r="W76">
-        <v>0.2266514283514284</v>
+        <v>0.2267734093067426</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3879801377680936</v>
+        <v>0.382807069264519</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2202634849561019</v>
+        <v>0.2221634849561019</v>
       </c>
       <c r="C77">
-        <v>-47.55132250118476</v>
+        <v>-49.54623378096197</v>
       </c>
       <c r="D77">
-        <v>48.24867749881524</v>
+        <v>47.81376621903803</v>
       </c>
       <c r="E77">
-        <v>100.4</v>
+        <v>101.96</v>
       </c>
       <c r="F77">
-        <v>117</v>
+        <v>118.56</v>
       </c>
       <c r="G77">
         <v>21.2</v>
@@ -7723,37 +7723,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M77">
-        <v>27.5886</v>
+        <v>27.956448</v>
       </c>
       <c r="N77">
-        <v>-17.02748888888889</v>
+        <v>-17.39533688888889</v>
       </c>
       <c r="O77">
-        <v>-1.702748888888889</v>
+        <v>-1.739533688888889</v>
       </c>
       <c r="P77">
-        <v>-15.32474</v>
+        <v>-15.6558032</v>
       </c>
       <c r="Q77">
-        <v>-13.77474</v>
+        <v>-14.1058032</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2007337119041797</v>
+        <v>0.2071892832335205</v>
       </c>
       <c r="T77">
-        <v>3.105438640417885</v>
+        <v>3.234831917101964</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03828070692645191</v>
+        <v>0.03777701341426175</v>
       </c>
       <c r="W77">
-        <v>0.2267734093067426</v>
+        <v>0.2268921802369171</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.382807069264519</v>
+        <v>0.3777701341426174</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2221634849561019</v>
+        <v>0.2240634849561019</v>
       </c>
       <c r="C78">
-        <v>-49.54623378096197</v>
+        <v>-51.53337456451968</v>
       </c>
       <c r="D78">
-        <v>47.81376621903803</v>
+        <v>47.38662543548033</v>
       </c>
       <c r="E78">
-        <v>101.96</v>
+        <v>103.52</v>
       </c>
       <c r="F78">
-        <v>118.56</v>
+        <v>120.12</v>
       </c>
       <c r="G78">
         <v>21.2</v>
@@ -7805,37 +7805,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M78">
-        <v>27.956448</v>
+        <v>28.324296</v>
       </c>
       <c r="N78">
-        <v>-17.39533688888889</v>
+        <v>-17.76318488888889</v>
       </c>
       <c r="O78">
-        <v>-1.739533688888889</v>
+        <v>-1.776318488888889</v>
       </c>
       <c r="P78">
-        <v>-15.6558032</v>
+        <v>-15.9868664</v>
       </c>
       <c r="Q78">
-        <v>-14.1058032</v>
+        <v>-14.4368664</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2071892832335205</v>
+        <v>0.2142062085914997</v>
       </c>
       <c r="T78">
-        <v>3.234831917101964</v>
+        <v>3.375476783062919</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03777701341426175</v>
+        <v>0.03728640285044016</v>
       </c>
       <c r="W78">
-        <v>0.2268921802369171</v>
+        <v>0.2270078662078662</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3777701341426174</v>
+        <v>0.3728640285044016</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2240634849561019</v>
+        <v>0.2259634849561019</v>
       </c>
       <c r="C79">
-        <v>-51.53337456451968</v>
+        <v>-53.51295125941016</v>
       </c>
       <c r="D79">
-        <v>47.38662543548033</v>
+        <v>46.96704874058985</v>
       </c>
       <c r="E79">
-        <v>103.52</v>
+        <v>105.08</v>
       </c>
       <c r="F79">
-        <v>120.12</v>
+        <v>121.68</v>
       </c>
       <c r="G79">
         <v>21.2</v>
@@ -7887,37 +7887,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M79">
-        <v>28.324296</v>
+        <v>28.692144</v>
       </c>
       <c r="N79">
-        <v>-17.76318488888889</v>
+        <v>-18.13103288888889</v>
       </c>
       <c r="O79">
-        <v>-1.776318488888889</v>
+        <v>-1.813103288888889</v>
       </c>
       <c r="P79">
-        <v>-15.9868664</v>
+        <v>-16.3179296</v>
       </c>
       <c r="Q79">
-        <v>-14.4368664</v>
+        <v>-14.7679296</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2142062085914997</v>
+        <v>0.2218610362547496</v>
       </c>
       <c r="T79">
-        <v>3.375476783062919</v>
+        <v>3.528907545929415</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03728640285044016</v>
+        <v>0.03680837204466529</v>
       </c>
       <c r="W79">
-        <v>0.2270078662078662</v>
+        <v>0.227120585871868</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3728640285044016</v>
+        <v>0.3680837204466529</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2259634849561019</v>
+        <v>0.2278634849561019</v>
       </c>
       <c r="C80">
-        <v>-53.51295125941016</v>
+        <v>-55.48516302694601</v>
       </c>
       <c r="D80">
-        <v>46.96704874058985</v>
+        <v>46.55483697305399</v>
       </c>
       <c r="E80">
-        <v>105.08</v>
+        <v>106.64</v>
       </c>
       <c r="F80">
-        <v>121.68</v>
+        <v>123.24</v>
       </c>
       <c r="G80">
         <v>21.2</v>
@@ -7969,37 +7969,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M80">
-        <v>28.692144</v>
+        <v>29.059992</v>
       </c>
       <c r="N80">
-        <v>-18.13103288888889</v>
+        <v>-18.49888088888889</v>
       </c>
       <c r="O80">
-        <v>-1.813103288888889</v>
+        <v>-1.84988808888889</v>
       </c>
       <c r="P80">
-        <v>-16.3179296</v>
+        <v>-16.64899280000001</v>
       </c>
       <c r="Q80">
-        <v>-14.7679296</v>
+        <v>-15.0989928</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2218610362547496</v>
+        <v>0.2302448951240235</v>
       </c>
       <c r="T80">
-        <v>3.528907545929415</v>
+        <v>3.696950762402245</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03680837204466529</v>
+        <v>0.03634244328460623</v>
       </c>
       <c r="W80">
-        <v>0.227120585871868</v>
+        <v>0.2272304518734899</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3680837204466529</v>
+        <v>0.3634244328460623</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2278634849561019</v>
+        <v>0.2297634849561019</v>
       </c>
       <c r="C81">
-        <v>-55.48516302694601</v>
+        <v>-57.45020209742106</v>
       </c>
       <c r="D81">
-        <v>46.55483697305399</v>
+        <v>46.14979790257896</v>
       </c>
       <c r="E81">
-        <v>106.64</v>
+        <v>108.2</v>
       </c>
       <c r="F81">
-        <v>123.24</v>
+        <v>124.8</v>
       </c>
       <c r="G81">
         <v>21.2</v>
@@ -8051,37 +8051,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M81">
-        <v>29.059992</v>
+        <v>29.42784</v>
       </c>
       <c r="N81">
-        <v>-18.49888088888889</v>
+        <v>-18.86672888888889</v>
       </c>
       <c r="O81">
-        <v>-1.84988808888889</v>
+        <v>-1.88667288888889</v>
       </c>
       <c r="P81">
-        <v>-16.64899280000001</v>
+        <v>-16.980056</v>
       </c>
       <c r="Q81">
-        <v>-15.0989928</v>
+        <v>-15.430056</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2302448951240235</v>
+        <v>0.2394671398802247</v>
       </c>
       <c r="T81">
-        <v>3.696950762402245</v>
+        <v>3.881798300522358</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03634244328460623</v>
+        <v>0.03588816274354866</v>
       </c>
       <c r="W81">
-        <v>0.2272304518734899</v>
+        <v>0.2273375712250712</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3634244328460623</v>
+        <v>0.3588816274354866</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2297634849561019</v>
+        <v>0.2316634849561019</v>
       </c>
       <c r="C82">
-        <v>-57.45020209742106</v>
+        <v>-59.40825406901791</v>
       </c>
       <c r="D82">
-        <v>46.14979790257896</v>
+        <v>45.7517459309821</v>
       </c>
       <c r="E82">
-        <v>108.2</v>
+        <v>109.76</v>
       </c>
       <c r="F82">
-        <v>124.8</v>
+        <v>126.36</v>
       </c>
       <c r="G82">
         <v>21.2</v>
@@ -8133,37 +8133,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M82">
-        <v>29.42784</v>
+        <v>29.79568800000001</v>
       </c>
       <c r="N82">
-        <v>-18.86672888888889</v>
+        <v>-19.2345768888889</v>
       </c>
       <c r="O82">
-        <v>-1.88667288888889</v>
+        <v>-1.92345768888889</v>
       </c>
       <c r="P82">
-        <v>-16.980056</v>
+        <v>-17.31111920000001</v>
       </c>
       <c r="Q82">
-        <v>-15.430056</v>
+        <v>-15.76111920000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2394671398802247</v>
+        <v>0.2496601472423417</v>
       </c>
       <c r="T82">
-        <v>3.881798300522358</v>
+        <v>4.08610347423406</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03588816274354866</v>
+        <v>0.03544509900597398</v>
       </c>
       <c r="W82">
-        <v>0.2273375712250712</v>
+        <v>0.2274420456543913</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3588816274354866</v>
+        <v>0.3544509900597398</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2316634849561019</v>
+        <v>0.233563484956102</v>
       </c>
       <c r="C83">
-        <v>-59.40825406901791</v>
+        <v>-61.3594981913792</v>
       </c>
       <c r="D83">
-        <v>45.7517459309821</v>
+        <v>45.36050180862081</v>
       </c>
       <c r="E83">
-        <v>109.76</v>
+        <v>111.32</v>
       </c>
       <c r="F83">
-        <v>126.36</v>
+        <v>127.92</v>
       </c>
       <c r="G83">
         <v>21.2</v>
@@ -8215,37 +8215,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M83">
-        <v>29.79568800000001</v>
+        <v>30.163536</v>
       </c>
       <c r="N83">
-        <v>-19.2345768888889</v>
+        <v>-19.60242488888889</v>
       </c>
       <c r="O83">
-        <v>-1.92345768888889</v>
+        <v>-1.960242488888889</v>
       </c>
       <c r="P83">
-        <v>-17.31111920000001</v>
+        <v>-17.6421824</v>
       </c>
       <c r="Q83">
-        <v>-15.76111920000001</v>
+        <v>-16.0921824</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2496601472423417</v>
+        <v>0.2609857109780274</v>
       </c>
       <c r="T83">
-        <v>4.08610347423406</v>
+        <v>4.31310922280262</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03544509900597398</v>
+        <v>0.03501284170102308</v>
       </c>
       <c r="W83">
-        <v>0.2274420456543913</v>
+        <v>0.2275439719268988</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3544509900597398</v>
+        <v>0.3501284170102308</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.233563484956102</v>
+        <v>0.2354634849561019</v>
       </c>
       <c r="C84">
-        <v>-61.3594981913792</v>
+        <v>-63.30410763475219</v>
       </c>
       <c r="D84">
-        <v>45.36050180862081</v>
+        <v>44.97589236524784</v>
       </c>
       <c r="E84">
-        <v>111.32</v>
+        <v>112.88</v>
       </c>
       <c r="F84">
-        <v>127.92</v>
+        <v>129.48</v>
       </c>
       <c r="G84">
         <v>21.2</v>
@@ -8297,37 +8297,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M84">
-        <v>30.163536</v>
+        <v>30.53138400000001</v>
       </c>
       <c r="N84">
-        <v>-19.60242488888889</v>
+        <v>-19.9702728888889</v>
       </c>
       <c r="O84">
-        <v>-1.960242488888889</v>
+        <v>-1.99702728888889</v>
       </c>
       <c r="P84">
-        <v>-17.6421824</v>
+        <v>-17.97324560000001</v>
       </c>
       <c r="Q84">
-        <v>-16.0921824</v>
+        <v>-16.4232456</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2609857109780274</v>
+        <v>0.2736436939767349</v>
       </c>
       <c r="T84">
-        <v>4.31310922280262</v>
+        <v>4.566821530026303</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03501284170102308</v>
+        <v>0.03459100023474569</v>
       </c>
       <c r="W84">
-        <v>0.2275439719268988</v>
+        <v>0.227643442144647</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3501284170102308</v>
+        <v>0.3459100023474569</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2354634849561019</v>
+        <v>0.2373634849561019</v>
       </c>
       <c r="C85">
-        <v>-63.30410763475219</v>
+        <v>-65.24224974555635</v>
       </c>
       <c r="D85">
-        <v>44.97589236524784</v>
+        <v>44.59775025444367</v>
       </c>
       <c r="E85">
-        <v>112.88</v>
+        <v>114.44</v>
       </c>
       <c r="F85">
-        <v>129.48</v>
+        <v>131.04</v>
       </c>
       <c r="G85">
         <v>21.2</v>
@@ -8379,37 +8379,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M85">
-        <v>30.53138400000001</v>
+        <v>30.899232</v>
       </c>
       <c r="N85">
-        <v>-19.9702728888889</v>
+        <v>-20.33812088888889</v>
       </c>
       <c r="O85">
-        <v>-1.99702728888889</v>
+        <v>-2.03381208888889</v>
       </c>
       <c r="P85">
-        <v>-17.97324560000001</v>
+        <v>-18.3043088</v>
       </c>
       <c r="Q85">
-        <v>-16.4232456</v>
+        <v>-16.7543088</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2736436939767349</v>
+        <v>0.2878839248502809</v>
       </c>
       <c r="T85">
-        <v>4.566821530026303</v>
+        <v>4.852247875652949</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03459100023474569</v>
+        <v>0.03417920261290348</v>
       </c>
       <c r="W85">
-        <v>0.227643442144647</v>
+        <v>0.2277405440238774</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3459100023474569</v>
+        <v>0.3417920261290348</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2373634849561019</v>
+        <v>0.2392634849561019</v>
       </c>
       <c r="C86">
-        <v>-65.24224974555632</v>
+        <v>-67.17408628916607</v>
       </c>
       <c r="D86">
-        <v>44.59775025444367</v>
+        <v>44.22591371083392</v>
       </c>
       <c r="E86">
-        <v>114.44</v>
+        <v>116</v>
       </c>
       <c r="F86">
-        <v>131.04</v>
+        <v>132.6</v>
       </c>
       <c r="G86">
         <v>21.2</v>
@@ -8461,37 +8461,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M86">
-        <v>30.899232</v>
+        <v>31.26708</v>
       </c>
       <c r="N86">
-        <v>-20.33812088888889</v>
+        <v>-20.70596888888889</v>
       </c>
       <c r="O86">
-        <v>-2.033812088888889</v>
+        <v>-2.070596888888889</v>
       </c>
       <c r="P86">
-        <v>-18.3043088</v>
+        <v>-18.635372</v>
       </c>
       <c r="Q86">
-        <v>-16.7543088</v>
+        <v>-17.085372</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2878839248502807</v>
+        <v>0.3040228531736328</v>
       </c>
       <c r="T86">
-        <v>4.852247875652945</v>
+        <v>5.175731067363142</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03417920261290349</v>
+        <v>0.03377709434686933</v>
       </c>
       <c r="W86">
-        <v>0.2277405440238774</v>
+        <v>0.2278353611530082</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3417920261290349</v>
+        <v>0.3377709434686933</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2392634849561019</v>
+        <v>0.2411634849561019</v>
       </c>
       <c r="C87">
-        <v>-67.17408628916607</v>
+        <v>-69.09977368064844</v>
       </c>
       <c r="D87">
-        <v>44.22591371083392</v>
+        <v>43.86022631935156</v>
       </c>
       <c r="E87">
-        <v>116</v>
+        <v>117.56</v>
       </c>
       <c r="F87">
-        <v>132.6</v>
+        <v>134.16</v>
       </c>
       <c r="G87">
         <v>21.2</v>
@@ -8543,37 +8543,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M87">
-        <v>31.26708</v>
+        <v>31.634928</v>
       </c>
       <c r="N87">
-        <v>-20.70596888888889</v>
+        <v>-21.07381688888889</v>
       </c>
       <c r="O87">
-        <v>-2.070596888888889</v>
+        <v>-2.107381688888889</v>
       </c>
       <c r="P87">
-        <v>-18.635372</v>
+        <v>-18.9664352</v>
       </c>
       <c r="Q87">
-        <v>-17.085372</v>
+        <v>-17.4164352</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3040228531736328</v>
+        <v>0.3224673426860352</v>
       </c>
       <c r="T87">
-        <v>5.175731067363142</v>
+        <v>5.545426143603366</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03377709434686933</v>
+        <v>0.03338433743585922</v>
       </c>
       <c r="W87">
-        <v>0.2278353611530082</v>
+        <v>0.2279279732326244</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3377709434686933</v>
+        <v>0.3338433743585921</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2411634849561019</v>
+        <v>0.2430634849561019</v>
       </c>
       <c r="C88">
-        <v>-69.09977368064844</v>
+        <v>-71.01946320414743</v>
       </c>
       <c r="D88">
-        <v>43.86022631935156</v>
+        <v>43.50053679585257</v>
       </c>
       <c r="E88">
-        <v>117.56</v>
+        <v>119.12</v>
       </c>
       <c r="F88">
-        <v>134.16</v>
+        <v>135.72</v>
       </c>
       <c r="G88">
         <v>21.2</v>
@@ -8625,37 +8625,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M88">
-        <v>31.634928</v>
+        <v>32.002776</v>
       </c>
       <c r="N88">
-        <v>-21.07381688888889</v>
+        <v>-21.44166488888889</v>
       </c>
       <c r="O88">
-        <v>-2.107381688888889</v>
+        <v>-2.14416648888889</v>
       </c>
       <c r="P88">
-        <v>-18.9664352</v>
+        <v>-19.29749840000001</v>
       </c>
       <c r="Q88">
-        <v>-17.4164352</v>
+        <v>-17.7474984</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3224673426860352</v>
+        <v>0.3437494459695763</v>
       </c>
       <c r="T88">
-        <v>5.545426143603366</v>
+        <v>5.97199738541901</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03338433743585922</v>
+        <v>0.03300060941935509</v>
       </c>
       <c r="W88">
-        <v>0.2279279732326244</v>
+        <v>0.2280184562989161</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3338433743585921</v>
+        <v>0.3300060941935509</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2430634849561019</v>
+        <v>0.2449634849561019</v>
       </c>
       <c r="C89">
-        <v>-71.01946320414743</v>
+        <v>-72.93330122156151</v>
       </c>
       <c r="D89">
-        <v>43.50053679585257</v>
+        <v>43.14669877843849</v>
       </c>
       <c r="E89">
-        <v>119.12</v>
+        <v>120.68</v>
       </c>
       <c r="F89">
-        <v>135.72</v>
+        <v>137.28</v>
       </c>
       <c r="G89">
         <v>21.2</v>
@@ -8707,37 +8707,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M89">
-        <v>32.002776</v>
+        <v>32.370624</v>
       </c>
       <c r="N89">
-        <v>-21.44166488888889</v>
+        <v>-21.80951288888889</v>
       </c>
       <c r="O89">
-        <v>-2.14416648888889</v>
+        <v>-2.180951288888889</v>
       </c>
       <c r="P89">
-        <v>-19.29749840000001</v>
+        <v>-19.6285616</v>
       </c>
       <c r="Q89">
-        <v>-17.7474984</v>
+        <v>-18.0785616</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3437494459695763</v>
+        <v>0.368578566467041</v>
       </c>
       <c r="T89">
-        <v>5.97199738541901</v>
+        <v>6.469663834203928</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03300060941935509</v>
+        <v>0.03262560249413515</v>
       </c>
       <c r="W89">
-        <v>0.2280184562989161</v>
+        <v>0.2281068829318829</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3300060941935509</v>
+        <v>0.3262560249413514</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2449634849561019</v>
+        <v>0.2468634849561019</v>
       </c>
       <c r="C90">
-        <v>-72.93330122156151</v>
+        <v>-74.84142937111858</v>
       </c>
       <c r="D90">
-        <v>43.14669877843849</v>
+        <v>42.79857062888143</v>
       </c>
       <c r="E90">
-        <v>120.68</v>
+        <v>122.24</v>
       </c>
       <c r="F90">
-        <v>137.28</v>
+        <v>138.84</v>
       </c>
       <c r="G90">
         <v>21.2</v>
@@ -8789,37 +8789,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M90">
-        <v>32.370624</v>
+        <v>32.738472</v>
       </c>
       <c r="N90">
-        <v>-21.80951288888889</v>
+        <v>-22.17736088888889</v>
       </c>
       <c r="O90">
-        <v>-2.180951288888889</v>
+        <v>-2.217736088888889</v>
       </c>
       <c r="P90">
-        <v>-19.6285616</v>
+        <v>-19.9596248</v>
       </c>
       <c r="Q90">
-        <v>-18.0785616</v>
+        <v>-18.4096248</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.368578566467041</v>
+        <v>0.3979220725094993</v>
       </c>
       <c r="T90">
-        <v>6.469663834203928</v>
+        <v>7.05781509185883</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03262560249413515</v>
+        <v>0.03225902269083025</v>
       </c>
       <c r="W90">
-        <v>0.2281068829318829</v>
+        <v>0.2281933224495022</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3262560249413514</v>
+        <v>0.3225902269083025</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2468634849561019</v>
+        <v>0.2487634849561019</v>
       </c>
       <c r="C91">
-        <v>-74.84142937111858</v>
+        <v>-76.74398475641497</v>
       </c>
       <c r="D91">
-        <v>42.79857062888143</v>
+        <v>42.45601524358504</v>
       </c>
       <c r="E91">
-        <v>122.24</v>
+        <v>123.8</v>
       </c>
       <c r="F91">
-        <v>138.84</v>
+        <v>140.4</v>
       </c>
       <c r="G91">
         <v>21.2</v>
@@ -8871,37 +8871,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M91">
-        <v>32.738472</v>
+        <v>33.10632</v>
       </c>
       <c r="N91">
-        <v>-22.17736088888889</v>
+        <v>-22.54520888888889</v>
       </c>
       <c r="O91">
-        <v>-2.217736088888889</v>
+        <v>-2.254520888888889</v>
       </c>
       <c r="P91">
-        <v>-19.9596248</v>
+        <v>-20.290688</v>
       </c>
       <c r="Q91">
-        <v>-18.4096248</v>
+        <v>-18.740688</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3979220725094993</v>
+        <v>0.4331342797604492</v>
       </c>
       <c r="T91">
-        <v>7.05781509185883</v>
+        <v>7.763596601044713</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03225902269083025</v>
+        <v>0.03190058910537658</v>
       </c>
       <c r="W91">
-        <v>0.2281933224495022</v>
+        <v>0.2282778410889522</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3225902269083025</v>
+        <v>0.3190058910537659</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2487634849561019</v>
+        <v>0.2506634849561019</v>
       </c>
       <c r="C92">
-        <v>-76.74398475641497</v>
+        <v>-78.64110012644812</v>
       </c>
       <c r="D92">
-        <v>42.45601524358504</v>
+        <v>42.11889987355188</v>
       </c>
       <c r="E92">
-        <v>123.8</v>
+        <v>125.36</v>
       </c>
       <c r="F92">
-        <v>140.4</v>
+        <v>141.96</v>
       </c>
       <c r="G92">
         <v>21.2</v>
@@ -8953,37 +8953,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M92">
-        <v>33.10632</v>
+        <v>33.47416800000001</v>
       </c>
       <c r="N92">
-        <v>-22.54520888888889</v>
+        <v>-22.9130568888889</v>
       </c>
       <c r="O92">
-        <v>-2.254520888888889</v>
+        <v>-2.29130568888889</v>
       </c>
       <c r="P92">
-        <v>-20.290688</v>
+        <v>-20.62175120000001</v>
       </c>
       <c r="Q92">
-        <v>-18.740688</v>
+        <v>-19.0717512</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4331342797604492</v>
+        <v>0.4761714219560547</v>
       </c>
       <c r="T92">
-        <v>7.763596601044713</v>
+        <v>8.626218445605238</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03190058910537658</v>
+        <v>0.03155003318114168</v>
       </c>
       <c r="W92">
-        <v>0.2282778410889522</v>
+        <v>0.2283605021758868</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3190058910537659</v>
+        <v>0.3155003318114168</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2506634849561019</v>
+        <v>0.2525634849561019</v>
       </c>
       <c r="C93">
-        <v>-78.64110012644812</v>
+        <v>-80.53290404713961</v>
       </c>
       <c r="D93">
-        <v>42.11889987355188</v>
+        <v>41.7870959528604</v>
       </c>
       <c r="E93">
-        <v>125.36</v>
+        <v>126.92</v>
       </c>
       <c r="F93">
-        <v>141.96</v>
+        <v>143.52</v>
       </c>
       <c r="G93">
         <v>21.2</v>
@@ -9035,37 +9035,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M93">
-        <v>33.47416800000001</v>
+        <v>33.842016</v>
       </c>
       <c r="N93">
-        <v>-22.9130568888889</v>
+        <v>-23.28090488888889</v>
       </c>
       <c r="O93">
-        <v>-2.29130568888889</v>
+        <v>-2.328090488888889</v>
       </c>
       <c r="P93">
-        <v>-20.62175120000001</v>
+        <v>-20.9528144</v>
       </c>
       <c r="Q93">
-        <v>-19.0717512</v>
+        <v>-19.4028144</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4761714219560547</v>
+        <v>0.5299678497005618</v>
       </c>
       <c r="T93">
-        <v>8.626218445605238</v>
+        <v>9.704495751305897</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03155003318114168</v>
+        <v>0.0312070980378684</v>
       </c>
       <c r="W93">
-        <v>0.2283605021758868</v>
+        <v>0.2284413662826706</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3155003318114168</v>
+        <v>0.312070980378684</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2525634849561019</v>
+        <v>0.2544634849561019</v>
       </c>
       <c r="C94">
-        <v>-80.53290404713961</v>
+        <v>-82.41952106481438</v>
       </c>
       <c r="D94">
-        <v>41.7870959528604</v>
+        <v>41.46047893518563</v>
       </c>
       <c r="E94">
-        <v>126.92</v>
+        <v>128.48</v>
       </c>
       <c r="F94">
-        <v>143.52</v>
+        <v>145.08</v>
       </c>
       <c r="G94">
         <v>21.2</v>
@@ -9117,37 +9117,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M94">
-        <v>33.842016</v>
+        <v>34.209864</v>
       </c>
       <c r="N94">
-        <v>-23.28090488888889</v>
+        <v>-23.64875288888889</v>
       </c>
       <c r="O94">
-        <v>-2.328090488888889</v>
+        <v>-2.364875288888889</v>
       </c>
       <c r="P94">
-        <v>-20.9528144</v>
+        <v>-21.2838776</v>
       </c>
       <c r="Q94">
-        <v>-19.4028144</v>
+        <v>-19.7338776</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5299678497005618</v>
+        <v>0.5991346853720706</v>
       </c>
       <c r="T94">
-        <v>9.704495751305897</v>
+        <v>11.09085228720674</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0312070980378684</v>
+        <v>0.03087153784391282</v>
       </c>
       <c r="W94">
-        <v>0.2284413662826706</v>
+        <v>0.2285204913764054</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.312070980378684</v>
+        <v>0.3087153784391282</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2544634849561019</v>
+        <v>0.2563634849561019</v>
       </c>
       <c r="C95">
-        <v>-82.41952106481438</v>
+        <v>-84.30107186207255</v>
       </c>
       <c r="D95">
-        <v>41.46047893518563</v>
+        <v>41.13892813792746</v>
       </c>
       <c r="E95">
-        <v>128.48</v>
+        <v>130.04</v>
       </c>
       <c r="F95">
-        <v>145.08</v>
+        <v>146.64</v>
       </c>
       <c r="G95">
         <v>21.2</v>
@@ -9199,37 +9199,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M95">
-        <v>34.209864</v>
+        <v>34.57771200000001</v>
       </c>
       <c r="N95">
-        <v>-23.64875288888889</v>
+        <v>-24.0166008888889</v>
       </c>
       <c r="O95">
-        <v>-2.364875288888889</v>
+        <v>-2.40166008888889</v>
       </c>
       <c r="P95">
-        <v>-21.2838776</v>
+        <v>-21.61494080000001</v>
       </c>
       <c r="Q95">
-        <v>-19.7338776</v>
+        <v>-20.06494080000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5991346853720706</v>
+        <v>0.6913571329340826</v>
       </c>
       <c r="T95">
-        <v>11.09085228720674</v>
+        <v>12.93932766840787</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03087153784391282</v>
+        <v>0.03054311722855205</v>
       </c>
       <c r="W95">
-        <v>0.2285204913764054</v>
+        <v>0.2285979329575074</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3087153784391282</v>
+        <v>0.3054311722855204</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2563634849561019</v>
+        <v>0.258263484956102</v>
       </c>
       <c r="C96">
-        <v>-84.30107186207255</v>
+        <v>-86.17767340646392</v>
       </c>
       <c r="D96">
-        <v>41.13892813792746</v>
+        <v>40.82232659353609</v>
       </c>
       <c r="E96">
-        <v>130.04</v>
+        <v>131.6</v>
       </c>
       <c r="F96">
-        <v>146.64</v>
+        <v>148.2</v>
       </c>
       <c r="G96">
         <v>21.2</v>
@@ -9281,37 +9281,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M96">
-        <v>34.57771200000001</v>
+        <v>34.94556000000001</v>
       </c>
       <c r="N96">
-        <v>-24.0166008888889</v>
+        <v>-24.3844488888889</v>
       </c>
       <c r="O96">
-        <v>-2.40166008888889</v>
+        <v>-2.43844488888889</v>
       </c>
       <c r="P96">
-        <v>-21.61494080000001</v>
+        <v>-21.94600400000001</v>
       </c>
       <c r="Q96">
-        <v>-20.06494080000001</v>
+        <v>-20.39600400000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6913571329340826</v>
+        <v>0.8204685595208994</v>
       </c>
       <c r="T96">
-        <v>12.93932766840787</v>
+        <v>15.52719320208945</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03054311722855205</v>
+        <v>0.03022161073140939</v>
       </c>
       <c r="W96">
-        <v>0.2285979329575074</v>
+        <v>0.2286737441895337</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3054311722855204</v>
+        <v>0.3022161073140939</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.258263484956102</v>
+        <v>0.2601634849561019</v>
       </c>
       <c r="C97">
-        <v>-86.17767340646392</v>
+        <v>-88.04943909234959</v>
       </c>
       <c r="D97">
-        <v>40.82232659353609</v>
+        <v>40.51056090765043</v>
       </c>
       <c r="E97">
-        <v>131.6</v>
+        <v>133.16</v>
       </c>
       <c r="F97">
-        <v>148.2</v>
+        <v>149.76</v>
       </c>
       <c r="G97">
         <v>21.2</v>
@@ -9363,37 +9363,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M97">
-        <v>34.94556000000001</v>
+        <v>35.313408</v>
       </c>
       <c r="N97">
-        <v>-24.3844488888889</v>
+        <v>-24.75229688888889</v>
       </c>
       <c r="O97">
-        <v>-2.43844488888889</v>
+        <v>-2.47522968888889</v>
       </c>
       <c r="P97">
-        <v>-21.94600400000001</v>
+        <v>-22.2770672</v>
       </c>
       <c r="Q97">
-        <v>-20.39600400000001</v>
+        <v>-20.7270672</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8204685595208994</v>
+        <v>1.014135699401125</v>
       </c>
       <c r="T97">
-        <v>15.52719320208945</v>
+        <v>19.40899150261182</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03022161073140939</v>
+        <v>0.02990680228629055</v>
       </c>
       <c r="W97">
-        <v>0.2286737441895337</v>
+        <v>0.2287479760208927</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3022161073140939</v>
+        <v>0.2990680228629055</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2601634849561019</v>
+        <v>0.2620634849561019</v>
       </c>
       <c r="C98">
-        <v>-88.04943909234956</v>
+        <v>-89.91647887631255</v>
       </c>
       <c r="D98">
-        <v>40.51056090765043</v>
+        <v>40.20352112368744</v>
       </c>
       <c r="E98">
-        <v>133.16</v>
+        <v>134.72</v>
       </c>
       <c r="F98">
-        <v>149.76</v>
+        <v>151.32</v>
       </c>
       <c r="G98">
         <v>21.2</v>
@@ -9445,37 +9445,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M98">
-        <v>35.313408</v>
+        <v>35.681256</v>
       </c>
       <c r="N98">
-        <v>-24.75229688888889</v>
+        <v>-25.12014488888889</v>
       </c>
       <c r="O98">
-        <v>-2.47522968888889</v>
+        <v>-2.512014488888889</v>
       </c>
       <c r="P98">
-        <v>-22.2770672</v>
+        <v>-22.6081304</v>
       </c>
       <c r="Q98">
-        <v>-20.7270672</v>
+        <v>-21.0581304</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.014135699401122</v>
+        <v>1.336914265868163</v>
       </c>
       <c r="T98">
-        <v>19.40899150261177</v>
+        <v>25.87865533681569</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02990680228629055</v>
+        <v>0.02959848473694735</v>
       </c>
       <c r="W98">
-        <v>0.2287479760208927</v>
+        <v>0.2288206772990278</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2990680228629055</v>
+        <v>0.2959848473694735</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2620634849561019</v>
+        <v>0.2639634849561019</v>
       </c>
       <c r="C99">
-        <v>-89.91647887631255</v>
+        <v>-91.77889940645666</v>
       </c>
       <c r="D99">
-        <v>40.20352112368744</v>
+        <v>39.90110059354334</v>
       </c>
       <c r="E99">
-        <v>134.72</v>
+        <v>136.28</v>
       </c>
       <c r="F99">
-        <v>151.32</v>
+        <v>152.88</v>
       </c>
       <c r="G99">
         <v>21.2</v>
@@ -9527,37 +9527,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M99">
-        <v>35.681256</v>
+        <v>36.049104</v>
       </c>
       <c r="N99">
-        <v>-25.12014488888889</v>
+        <v>-25.48799288888889</v>
       </c>
       <c r="O99">
-        <v>-2.512014488888889</v>
+        <v>-2.548799288888889</v>
       </c>
       <c r="P99">
-        <v>-22.6081304</v>
+        <v>-22.9391936</v>
       </c>
       <c r="Q99">
-        <v>-21.0581304</v>
+        <v>-21.3891936</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.336914265868163</v>
+        <v>1.982471398802244</v>
       </c>
       <c r="T99">
-        <v>25.87865533681569</v>
+        <v>38.81798300522353</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02959848473694735</v>
+        <v>0.0292964593824887</v>
       </c>
       <c r="W99">
-        <v>0.2288206772990278</v>
+        <v>0.2288918948776092</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2959848473694735</v>
+        <v>0.292964593824887</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2639634849561019</v>
+        <v>0.2658634849561019</v>
       </c>
       <c r="C100">
-        <v>-91.77889940645666</v>
+        <v>-93.63680414591336</v>
       </c>
       <c r="D100">
-        <v>39.90110059354334</v>
+        <v>39.60319585408664</v>
       </c>
       <c r="E100">
-        <v>136.28</v>
+        <v>137.84</v>
       </c>
       <c r="F100">
-        <v>152.88</v>
+        <v>154.44</v>
       </c>
       <c r="G100">
         <v>21.2</v>
@@ -9609,37 +9609,37 @@
         <v>10.56111111111111</v>
       </c>
       <c r="M100">
-        <v>36.049104</v>
+        <v>36.416952</v>
       </c>
       <c r="N100">
-        <v>-25.48799288888889</v>
+        <v>-25.85584088888889</v>
       </c>
       <c r="O100">
-        <v>-2.548799288888889</v>
+        <v>-2.585584088888889</v>
       </c>
       <c r="P100">
-        <v>-22.9391936</v>
+        <v>-23.2702568</v>
       </c>
       <c r="Q100">
-        <v>-21.3891936</v>
+        <v>-21.7202568</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.982471398802244</v>
+        <v>3.919142797604489</v>
       </c>
       <c r="T100">
-        <v>38.81798300522353</v>
+        <v>77.63596601044706</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0292964593824887</v>
+        <v>0.02900053555034235</v>
       </c>
       <c r="W100">
-        <v>0.2288918948776092</v>
+        <v>0.2289616737172293</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.292964593824887</v>
+        <v>0.2900053555034235</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2658634849561019</v>
-      </c>
-      <c r="C101">
-        <v>-93.63680414591336</v>
-      </c>
-      <c r="D101">
-        <v>39.60319585408664</v>
-      </c>
-      <c r="E101">
-        <v>137.84</v>
-      </c>
-      <c r="F101">
-        <v>154.44</v>
-      </c>
-      <c r="G101">
-        <v>21.2</v>
-      </c>
-      <c r="H101">
-        <v>139.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>12.11111111111111</v>
-      </c>
-      <c r="K101">
-        <v>1.55</v>
-      </c>
-      <c r="L101">
-        <v>10.56111111111111</v>
-      </c>
-      <c r="M101">
-        <v>36.416952</v>
-      </c>
-      <c r="N101">
-        <v>-25.85584088888889</v>
-      </c>
-      <c r="O101">
-        <v>-2.585584088888889</v>
-      </c>
-      <c r="P101">
-        <v>-23.2702568</v>
-      </c>
-      <c r="Q101">
-        <v>-21.7202568</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.919142797604489</v>
-      </c>
-      <c r="T101">
-        <v>77.63596601044706</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02900053555034235</v>
-      </c>
-      <c r="W101">
-        <v>0.2289616737172293</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2900053555034235</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
